--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R4fd4afc41cf944e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geometry" sheetId="2" r:id="Rb160c8f52add41ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="3" r:id="Rc066ef1603194c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="R5948c8af134446ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal spans" sheetId="5" r:id="R7ca8a6201c5d4062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluids" sheetId="6" r:id="Ra14d2b1473d1488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="7" r:id="Ra0b132a87e9947d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model choices" sheetId="8" r:id="Rb3dcaa9871fe421b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form pipe" sheetId="9" r:id="Rbd1beffc2d7d4f47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form sensor" sheetId="10" r:id="R9cdf0136f50a449e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form material" sheetId="11" r:id="Raf88f99e746a4296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="12" r:id="Rf133fd7bc31040a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase requests" sheetId="13" r:id="Rbc3cd00ee05f4c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review issues" sheetId="14" r:id="R18074aadc6c14b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R079a58e935414fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R3d2f3e7467d64bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geometry" sheetId="2" r:id="R6ca0c0b358174654"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="3" r:id="Rcd6a7b01ec60446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="Raa4e924a0d4b4380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal spans" sheetId="5" r:id="R95557c7300554084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluids" sheetId="6" r:id="Rd1a195450d0244f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="7" r:id="R3e74bcec881d4e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model choices" sheetId="8" r:id="Rd8f76f5a2f7d42a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form pipe" sheetId="9" r:id="R041235539c544b35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form sensor" sheetId="10" r:id="R44dff52537404fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form material" sheetId="11" r:id="Rca46a8c6c1d745b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="12" r:id="Rfab6aefbf3614370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase requests" sheetId="13" r:id="R577337ec05494dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review issues" sheetId="14" r:id="R38d66bb972ee4719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rfabdf3b6caae4c4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -497,7 +497,7 @@
         <x:v>Configuration ID</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>VCU-REV9-DRAFT-001</x:v>
+        <x:v>VCU-REV9-DRAFT-002</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
         <x:v>Change after physical configuration changes.</x:v>
@@ -625,7 +625,7 @@
         <x:v>Output refresh</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>Package maintainer: see START_HERE.md</x:v>
+        <x:v>Upload to GitHub; Actions builds the PDF. See support/docs/DATED_CHECKPOINTS.md.</x:v>
       </x:c>
       <x:c r="C19" s="8" t="str">
         <x:v>The experimental team can complete forms without running scripts.</x:v>
@@ -651,6 +651,28 @@
       </x:c>
       <x:c r="C21" s="8" t="str">
         <x:v>Assign the circuit and operating range for each experiment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="38" customHeight="1">
+      <x:c r="A22" s="9" t="str">
+        <x:v>Effective date</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="str">
+        <x:v>2026-10-16</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="str">
+        <x:v>Date this documentation configuration takes effect; ISO YYYY-MM-DD text.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="9" t="str">
+        <x:v>Change summary</x:v>
+      </x:c>
+      <x:c r="B23" s="9" t="str">
+        <x:v>PTC-X removed from active sensor and calibration records at the repository owner's request. Documentation change only; no physical removal or installed-hardware verification is asserted.</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="str">
+        <x:v>Describe changes since the preceding configuration and identify evidence or the request.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1790,19 +1812,19 @@
         <x:v>Campaign execution conventions; proposed revision log</x:v>
       </x:c>
       <x:c r="I7" s="17" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>2026-10-16 / VCU-REV9-DRAFT-002: PTC-X removed from active sensor and calibration records at the repository owner's request. Documentation change only; no physical removal or installed-hardware verification is asserted.</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Reported</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
-        <x:v>None supplied</x:v>
+        <x:v>USER</x:v>
       </x:c>
       <x:c r="L7" s="17" t="str">
-        <x:v>Not available</x:v>
+        <x:v>Repository owner request in the Codex session, 2026-10-16; Start effective date and change summary.</x:v>
       </x:c>
       <x:c r="M7" s="17" t="str">
-        <x:v>Needs information</x:v>
+        <x:v>Needs review</x:v>
       </x:c>
       <x:c r="N7" s="17" t="str">
         <x:v>Record effective date, author, changed item, reason, previous/new evidence, affected runs and whether recalibration or model revalidation is needed.</x:v>
@@ -2717,7 +2739,7 @@
         <x:v>Needs review</x:v>
       </x:c>
       <x:c r="N26" s="17" t="str">
-        <x:v>Confirm installed count and resolve PTC-X; no channel identity inferred.</x:v>
+        <x:v>Verify installed hardware count and channel identities for remaining sensors. PTC-X was removed from the active register at the repository owner's request on 2026-10-16; no physical removal is asserted.</x:v>
       </x:c>
       <x:c r="O26" s="19"/>
       <x:c r="P26" s="19"/>
@@ -5468,7 +5490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3c4af1978db4fbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2093fdc13f34801"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5631,7 +5653,7 @@
         <x:v>P0 Method: instrumentation</x:v>
       </x:c>
       <x:c r="I7" s="17" t="str">
-        <x:v>Resolve PTC-X; do not copy CAD IDs or assume TC/Luna co-location.</x:v>
+        <x:v>PTC-X omitted from the active register by owner request, 2026-10-16. Verify remaining installed sensor identities; do not assume CAD IDs are DAQ channels or TC/Luna co-location.</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
         <x:v>Evidence supplied and reviewed; open limitations recorded.</x:v>
@@ -6120,7 +6142,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd89ff63fa3604e25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5944131610884552"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6281,13 +6303,13 @@
         <x:v>R9 sheets 5-6; SNOTE VCU Rev9 PTCX note</x:v>
       </x:c>
       <x:c r="D9" s="17" t="str">
-        <x:v>CAD extraction includes PTC-X; note calls PTCX a fluke.</x:v>
+        <x:v>Historical CAD extraction includes PTC-X; the supplied note calls PTCX a fluke. PTC-X was removed from the active sensor/calibration records by owner request, 2026-10-16. Installed hardware identity is unverified.</x:v>
       </x:c>
       <x:c r="E9" s="17" t="str">
         <x:v>Experimental instrumentation</x:v>
       </x:c>
       <x:c r="F9" s="17" t="str">
-        <x:v>Check installed hardware and source labeling; keep unresolved reference until dispositioned.</x:v>
+        <x:v>Retain the original CAD/source evidence. Confirm whether the excluded reference corresponds to installed hardware before using it in any run or model mapping.</x:v>
       </x:c>
       <x:c r="G9" s="17" t="str">
         <x:v>C21; C23</x:v>
@@ -6411,7 +6433,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a88f358128c49c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab575658e8534009"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6768,7 +6790,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R368ebb592a1a4c9b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R866c82e6ea2645b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7803,36 +7825,18 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="8" t="str">
-        <x:v>PTC-X</x:v>
-      </x:c>
-      <x:c r="B21" s="8" t="str">
-        <x:v>PTC</x:v>
-      </x:c>
-      <x:c r="C21" s="8" t="str">
-        <x:v>downcomer</x:v>
-      </x:c>
-      <x:c r="D21" s="8" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="E21" s="10" t="n">
-        <x:v>50.799998652460545</x:v>
-      </x:c>
+      <x:c r="A21" s="8"/>
+      <x:c r="B21" s="8"/>
+      <x:c r="C21" s="8"/>
+      <x:c r="D21" s="8"/>
+      <x:c r="E21" s="10"/>
       <x:c r="F21" s="10"/>
       <x:c r="G21" s="10"/>
       <x:c r="H21" s="8"/>
-      <x:c r="I21" s="8" t="str">
-        <x:v>CAD-derived</x:v>
-      </x:c>
-      <x:c r="J21" s="8" t="str">
-        <x:v>Mount reference</x:v>
-      </x:c>
-      <x:c r="K21" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L21" s="8" t="str">
-        <x:v>Conflicts with note: PTCX is a fluke; verify installed hardware.</x:v>
-      </x:c>
+      <x:c r="I21" s="8"/>
+      <x:c r="J21" s="8"/>
+      <x:c r="K21" s="8"/>
+      <x:c r="L21" s="8"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
       <x:c r="A22" s="8" t="str">
@@ -8397,9 +8401,7 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="8" t="str">
-        <x:v>PTC-X</x:v>
-      </x:c>
+      <x:c r="A21" s="8"/>
       <x:c r="B21" s="8"/>
       <x:c r="C21" s="8"/>
       <x:c r="D21" s="8"/>
@@ -8410,9 +8412,7 @@
       <x:c r="I21" s="8"/>
       <x:c r="J21" s="8"/>
       <x:c r="K21" s="8"/>
-      <x:c r="L21" s="8" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
+      <x:c r="L21" s="8"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
       <x:c r="A22" s="8" t="str">

--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R3d2f3e7467d64bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geometry" sheetId="2" r:id="R6ca0c0b358174654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="3" r:id="Rcd6a7b01ec60446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="Raa4e924a0d4b4380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal spans" sheetId="5" r:id="R95557c7300554084"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluids" sheetId="6" r:id="Rd1a195450d0244f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="7" r:id="R3e74bcec881d4e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model choices" sheetId="8" r:id="Rd8f76f5a2f7d42a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form pipe" sheetId="9" r:id="R041235539c544b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form sensor" sheetId="10" r:id="R44dff52537404fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form material" sheetId="11" r:id="Rca46a8c6c1d745b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="12" r:id="Rfab6aefbf3614370"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase requests" sheetId="13" r:id="R577337ec05494dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review issues" sheetId="14" r:id="R38d66bb972ee4719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rfabdf3b6caae4c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="Rdb02ed5692054212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geometry" sheetId="2" r:id="Rf1a1c2c29ae74f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="3" r:id="R8cf742f24a1242b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="Rce9e1ed27a584c06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal spans" sheetId="5" r:id="R71573f0f7a2441c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluids" sheetId="6" r:id="R1ed7dc31f52e48ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="7" r:id="R9eb6acc318f84a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model choices" sheetId="8" r:id="R7829d47b1a094173"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form pipe" sheetId="9" r:id="R8e46e6eef5be4265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form sensor" sheetId="10" r:id="R0033565f60de4b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form material" sheetId="11" r:id="R22ed0c6c434a4896"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="12" r:id="R187ac51e51ea41b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase requests" sheetId="13" r:id="Rcd7df112b25b46dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review issues" sheetId="14" r:id="Rdade0e14c7f84263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R598c4ac295604744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insulation regions" sheetId="16" r:id="R0557123f889541bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="0.000"/>
+    <x:numFmt numFmtId="201" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -64,8 +66,25 @@
       <x:color rgb="FF576976"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203D4C"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -97,6 +116,21 @@
         <x:fgColor rgb="FFFFF4D6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF16374A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF3F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -110,7 +144,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -166,6 +200,41 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -497,7 +566,7 @@
         <x:v>Configuration ID</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>VCU-REV9-DRAFT-002</x:v>
+        <x:v>VCU-REV9-DRAFT-003</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
         <x:v>Change after physical configuration changes.</x:v>
@@ -614,7 +683,7 @@
         <x:v>Editing sequence</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>Start with Form pipe, Form sensor and Form material</x:v>
+        <x:v>Start with Form tabs, or Insulation regions for whole-region coverage.</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
         <x:v>Read the reference; enter new evidence in amber cells; send for review.</x:v>
@@ -669,7 +738,7 @@
         <x:v>Change summary</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>PTC-X removed from active sensor and calibration records at the repository owner's request. Documentation change only; no physical removal or installed-hardware verification is asserted.</x:v>
+        <x:v>Added ten insulation regions, coverage dropdowns and a separate diagram. All coverage starts Unknown pending evidence. PTC-X remains excluded from the active register.</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
         <x:v>Describe changes since the preceding configuration and identify evidence or the request.</x:v>
@@ -1812,7 +1881,7 @@
         <x:v>Campaign execution conventions; proposed revision log</x:v>
       </x:c>
       <x:c r="I7" s="17" t="str">
-        <x:v>2026-10-16 / VCU-REV9-DRAFT-002: PTC-X removed from active sensor and calibration records at the repository owner's request. Documentation change only; no physical removal or installed-hardware verification is asserted.</x:v>
+        <x:v>2026-10-16 / VCU-REV9-DRAFT-002: PTC-X removed from active sensor and calibration records at the repository owner's request. Documentation change only; no physical removal or installed-hardware verification is asserted. 2026-10-16 / VCU-REV9-DRAFT-003: added ten insulation coverage regions and the diagram; all coverage Unknown pending evidence.</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
         <x:v>Reported</x:v>
@@ -1821,7 +1890,7 @@
         <x:v>USER</x:v>
       </x:c>
       <x:c r="L7" s="17" t="str">
-        <x:v>Repository owner request in the Codex session, 2026-10-16; Start effective date and change summary.</x:v>
+        <x:v>Start effective date and change summary; previous record saved at support/checkpoints/2026-10-16_VCU-REV9-DRAFT-002/. Owner-approved insulation feature plan in the Codex session, 2026-10-16; installed coverage remains unconfirmed.</x:v>
       </x:c>
       <x:c r="M7" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -5490,7 +5559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2093fdc13f34801"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe3645e732ce4448"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6211,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5944131610884552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efd2b3592534634"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6433,7 +6502,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab575658e8534009"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9e02aec8f064b4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6790,8 +6859,402 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R866c82e6ea2645b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd789b6a13c34804"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="B1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="C1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="F1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="G1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="H1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+      <x:c r="I1" s="29" t="str">
+        <x:v>Insulation coverage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="29" customHeight="1">
+      <x:c r="A2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="B2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="C2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="D2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="E2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="F2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="G2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="H2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+      <x:c r="I2" s="30" t="str">
+        <x:v>Choose Unknown, Insulated or Bare for each whole region. Gray cells identify the region; amber cells are editable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="29" customHeight="1">
+      <x:c r="A3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="B3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="C3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="D3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="E3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="F3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="G3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="H3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+      <x:c r="I3" s="30" t="str">
+        <x:v>Material ID refers to the Materials tab. Thickness is in mm. Add evidence and identify the insulated surface, particularly around the cooler jacket.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="29" customHeight="1">
+      <x:c r="A4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="B4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="C4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="D4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="E4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="F4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="G4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="H4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+      <x:c r="I4" s="30" t="str">
+        <x:v>Pre/post follow drawing traversal. Top boundaries come from Complete jacket on Thermal spans; corners are schematic. Upload the workbook to rebuild the PDF.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
+      <x:c r="A5" s="31" t="str">
+        <x:v>Region ID</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Region</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>Boundary reference</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>Coverage</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>Material ID</x:v>
+      </x:c>
+      <x:c r="F5" s="31" t="str">
+        <x:v>Thickness mm</x:v>
+      </x:c>
+      <x:c r="G5" s="31" t="str">
+        <x:v>Evidence type</x:v>
+      </x:c>
+      <x:c r="H5" s="31" t="str">
+        <x:v>Evidence file / location</x:v>
+      </x:c>
+      <x:c r="I5" s="31" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="32" t="str">
+        <x:v>INS-01</x:v>
+      </x:c>
+      <x:c r="B6" s="32" t="str">
+        <x:v>Upcomer</x:v>
+      </x:c>
+      <x:c r="C6" s="32" t="str">
+        <x:v>Full segment</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E6" s="33"/>
+      <x:c r="F6" s="34"/>
+      <x:c r="G6" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H6" s="33"/>
+      <x:c r="I6" s="33"/>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="32" t="str">
+        <x:v>INS-02</x:v>
+      </x:c>
+      <x:c r="B7" s="32" t="str">
+        <x:v>Top-left corner</x:v>
+      </x:c>
+      <x:c r="C7" s="32" t="str">
+        <x:v>Full schematic corner</x:v>
+      </x:c>
+      <x:c r="D7" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E7" s="33"/>
+      <x:c r="F7" s="34"/>
+      <x:c r="G7" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H7" s="33"/>
+      <x:c r="I7" s="33"/>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="32" t="str">
+        <x:v>INS-03</x:v>
+      </x:c>
+      <x:c r="B8" s="32" t="str">
+        <x:v>Pre-cooler</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="str">
+        <x:v>Segment start to Complete jacket start</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E8" s="33"/>
+      <x:c r="F8" s="34"/>
+      <x:c r="G8" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H8" s="33"/>
+      <x:c r="I8" s="33"/>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="32" t="str">
+        <x:v>INS-04</x:v>
+      </x:c>
+      <x:c r="B9" s="32" t="str">
+        <x:v>Cooler</x:v>
+      </x:c>
+      <x:c r="C9" s="32" t="str">
+        <x:v>Complete jacket start to Complete jacket end</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E9" s="33"/>
+      <x:c r="F9" s="34"/>
+      <x:c r="G9" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H9" s="33"/>
+      <x:c r="I9" s="33" t="str">
+        <x:v>Identify the insulated surface, especially jacket exterior versus pipe.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="32" t="str">
+        <x:v>INS-05</x:v>
+      </x:c>
+      <x:c r="B10" s="32" t="str">
+        <x:v>Post-cooler</x:v>
+      </x:c>
+      <x:c r="C10" s="32" t="str">
+        <x:v>Complete jacket end to segment end</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E10" s="33"/>
+      <x:c r="F10" s="34"/>
+      <x:c r="G10" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H10" s="33"/>
+      <x:c r="I10" s="33"/>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="32" t="str">
+        <x:v>INS-06</x:v>
+      </x:c>
+      <x:c r="B11" s="32" t="str">
+        <x:v>Top-right corner</x:v>
+      </x:c>
+      <x:c r="C11" s="32" t="str">
+        <x:v>Full schematic corner</x:v>
+      </x:c>
+      <x:c r="D11" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E11" s="33"/>
+      <x:c r="F11" s="34"/>
+      <x:c r="G11" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H11" s="33"/>
+      <x:c r="I11" s="33"/>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="32" t="str">
+        <x:v>INS-07</x:v>
+      </x:c>
+      <x:c r="B12" s="32" t="str">
+        <x:v>Downcomer</x:v>
+      </x:c>
+      <x:c r="C12" s="32" t="str">
+        <x:v>Full segment</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E12" s="33"/>
+      <x:c r="F12" s="34"/>
+      <x:c r="G12" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H12" s="33"/>
+      <x:c r="I12" s="33"/>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="32" t="str">
+        <x:v>INS-08</x:v>
+      </x:c>
+      <x:c r="B13" s="32" t="str">
+        <x:v>Bottom-right corner</x:v>
+      </x:c>
+      <x:c r="C13" s="32" t="str">
+        <x:v>Full schematic corner</x:v>
+      </x:c>
+      <x:c r="D13" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E13" s="33"/>
+      <x:c r="F13" s="34"/>
+      <x:c r="G13" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H13" s="33"/>
+      <x:c r="I13" s="33"/>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="32" t="str">
+        <x:v>INS-09</x:v>
+      </x:c>
+      <x:c r="B14" s="32" t="str">
+        <x:v>Heater</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="str">
+        <x:v>Full segment</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E14" s="33"/>
+      <x:c r="F14" s="34"/>
+      <x:c r="G14" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H14" s="33"/>
+      <x:c r="I14" s="33"/>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="32" t="str">
+        <x:v>INS-10</x:v>
+      </x:c>
+      <x:c r="B15" s="32" t="str">
+        <x:v>Bottom-left corner</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="str">
+        <x:v>Full schematic corner</x:v>
+      </x:c>
+      <x:c r="D15" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="E15" s="33"/>
+      <x:c r="F15" s="34"/>
+      <x:c r="G15" s="33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="H15" s="33"/>
+      <x:c r="I15" s="33"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A3:I3"/>
+    <x:mergeCell ref="A4:I4"/>
+  </x:mergeCells>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="D6:D15">
+      <x:formula1>"Unknown,Insulated,Bare"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G6:G15">
+      <x:formula1>"Unknown,CAD-derived,Installed measurement,Reported,Modeling assumption"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="F6:F15">
+      <x:formula1>0</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 

--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="Rdb02ed5692054212"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geometry" sheetId="2" r:id="Rf1a1c2c29ae74f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="3" r:id="R8cf742f24a1242b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="Rce9e1ed27a584c06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal spans" sheetId="5" r:id="R71573f0f7a2441c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluids" sheetId="6" r:id="R1ed7dc31f52e48ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="7" r:id="R9eb6acc318f84a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model choices" sheetId="8" r:id="R7829d47b1a094173"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form pipe" sheetId="9" r:id="R8e46e6eef5be4265"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form sensor" sheetId="10" r:id="R0033565f60de4b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form material" sheetId="11" r:id="R22ed0c6c434a4896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="12" r:id="R187ac51e51ea41b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase requests" sheetId="13" r:id="Rcd7df112b25b46dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review issues" sheetId="14" r:id="Rdade0e14c7f84263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R598c4ac295604744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insulation regions" sheetId="16" r:id="R0557123f889541bd"/>
+    <x:sheet name="Start" sheetId="1" r:id="Rdb02ed5692054212"/>
+    <x:sheet name="Geometry" sheetId="2" r:id="Rf1a1c2c29ae74f1d"/>
+    <x:sheet name="Sensors" sheetId="3" r:id="R8cf742f24a1242b4"/>
+    <x:sheet name="Calibration" sheetId="4" r:id="Rce9e1ed27a584c06"/>
+    <x:sheet name="Thermal spans" sheetId="5" r:id="R71573f0f7a2441c6"/>
+    <x:sheet name="Fluids" sheetId="6" r:id="R1ed7dc31f52e48ce"/>
+    <x:sheet name="Materials" sheetId="7" r:id="R9eb6acc318f84a13"/>
+    <x:sheet name="Model choices" sheetId="8" r:id="R7829d47b1a094173"/>
+    <x:sheet name="Form pipe" sheetId="9" r:id="R8e46e6eef5be4265"/>
+    <x:sheet name="Form sensor" sheetId="10" r:id="R0033565f60de4b42"/>
+    <x:sheet name="Form material" sheetId="11" r:id="R22ed0c6c434a4896"/>
+    <x:sheet name="Requirements" sheetId="12" r:id="R187ac51e51ea41b6"/>
+    <x:sheet name="Phase requests" sheetId="13" r:id="Rcd7df112b25b46dd"/>
+    <x:sheet name="Review issues" sheetId="14" r:id="Rdade0e14c7f84263"/>
+    <x:sheet name="Sources" sheetId="15" r:id="R598c4ac295604744"/>
+    <x:sheet name="Insulation regions" sheetId="16" r:id="R0557123f889541bd"/>
+    <x:sheet name="CAD dimensions" sheetId="17" r:id="rIdCFG001Dimensions"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -506,6 +507,470 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/cfg001_dimensions.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="86" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="112" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="11" t="inlineStr">
+        <x:is>
+          <x:t>VCU Rev9 component reference dimensions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="12" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived local dimensions; not installed measurements. Main bore unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="11"/>
+      <x:c r="C2" s="11"/>
+      <x:c r="D2" s="11"/>
+      <x:c r="E2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="13" t="inlineStr">
+        <x:is>
+          <x:t>Use local bores only for the identified component. Portable source: support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="11"/>
+      <x:c r="C3" s="11"/>
+      <x:c r="D3" s="11"/>
+      <x:c r="E3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="11"/>
+      <x:c r="B4" s="11"/>
+      <x:c r="C4" s="11"/>
+      <x:c r="D4" s="11"/>
+      <x:c r="E4" s="11"/>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
+      <x:c r="A5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Record ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Component</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Reference values</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Units</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Evidence / limitations</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="110" customHeight="1">
+      <x:c r="A6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Main swept loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=33.401</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Main swept loop; Both main-loop definitions have only the outer pipe envelope. Main bore absent.; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F6</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="110" customHeight="1">
+      <x:c r="A7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>TLEP / BREP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=33.401; inner_diameter_mm=26.924; wall_thickness_mm=3.238500000000002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / TLEP / BREP; Annular exit tube cylinders; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F2 / F1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="110" customHeight="1">
+      <x:c r="A8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Cooling jacket shell</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=88.9; inner_diameter_mm=77.9272; wall_thickness_mm=5.486400000000003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Cooling jacket shell; Concentric shell cylinders; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F4 / F3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="110" customHeight="1">
+      <x:c r="A9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Jacket end plates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=88.9; inner_diameter_mm=33.655; radial_width_mm=27.622500000000002; axial_thickness_mm=6.35</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Jacket end plates; Inner diameter is the pipe clearance hole, not coolant-annulus diameter; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F2 / F1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="110" customHeight="1">
+      <x:c r="A10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-05</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Jacket port nipples</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=33.401; inner_diameter_mm=26.6446; wall_thickness_mm=3.3782000000000014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Jacket port nipples; OD is cylindrical land; thread shape is not represented by this value; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F1 / F27</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="110" customHeight="1">
+      <x:c r="A11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-06</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>HX hoses</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=35.814</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / HX hoses; Solid swept envelope; hose bore absent; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="110" customHeight="1">
+      <x:c r="A12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-07</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Drain-valve body</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=42.545; inner_diameter_mm=34.671; wall_thickness_mm=3.937000000000001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Drain-valve body; Simplified body, multiple intersecting cylinder spans; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F7 / F2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="110" customHeight="1">
+      <x:c r="A13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-08</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>LF / combined sensor spools</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=33.401; inner_diameter_mm=26.6446; wall_thickness_mm=3.3782000000000014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / LF / combined sensor spools; Local spool dimensions; do not apply bore globally; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F5 / F4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="110" customHeight="1">
+      <x:c r="A14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-09</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC / JTC mount spools</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=33.528; inner_diameter_mm=25.4; wall_thickness_mm=4.064</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / PTC / JTC mount spools; Local 76.2 mm spool; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F3 / F2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="110" customHeight="1">
+      <x:c r="A15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>TC sheath</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=3.175</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / TC sheath; External sheath only; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="110" customHeight="1">
+      <x:c r="A16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC guide tubing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=6.35; inner_diameter_mm=4.572; wall_thickness_mm=0.8889999999999998</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / PTC guide tubing; Local instrument tubing; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F1 / F2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="110" customHeight="1">
+      <x:c r="A17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>LF guide tubing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=6.35; inner_diameter_mm=3.8608; wall_thickness_mm=1.2446</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / LF guide tubing; Local instrument tubing; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F1 / F2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="110" customHeight="1">
+      <x:c r="A18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-13</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Fiber capillary tubing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=1.5875; inner_diameter_mm=1.0922; wall_thickness_mm=0.24764999999999993</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Fiber capillary tubing; Local optical capillary tubing; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F1 / F2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="110" customHeight="1">
+      <x:c r="A19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIM-14</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Expansion tank shell</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>outer_diameter_mm=203.2; inner_diameter_mm=198.09378228810465; wall_thickness_mm=2.55310885594767</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived; DIA / Expansion tank shell; Outer axial span 311.15 mm; support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Diameters.csv / F2 / F1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="Rbd789b6a13c34804"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -565,8 +1030,10 @@
       <x:c r="A7" s="8" t="str">
         <x:v>Configuration ID</x:v>
       </x:c>
-      <x:c r="B7" s="9" t="str">
-        <x:v>VCU-REV9-DRAFT-003</x:v>
+      <x:c r="B7" s="9" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-004</x:t>
+        </x:is>
       </x:c>
       <x:c r="C7" s="8" t="str">
         <x:v>Change after physical configuration changes.</x:v>
@@ -664,7 +1131,11 @@
       <x:c r="A16" s="8" t="str">
         <x:v>Prepared by</x:v>
       </x:c>
-      <x:c r="B16" s="9"/>
+      <x:c r="B16" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Codex; VCU reference synchronization requested by Andres Fierro</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C16" s="8" t="str">
         <x:v>Enter name.</x:v>
       </x:c>
@@ -737,8 +1208,10 @@
       <x:c r="A23" s="9" t="str">
         <x:v>Change summary</x:v>
       </x:c>
-      <x:c r="B23" s="9" t="str">
-        <x:v>Added ten insulation regions, coverage dropdowns and a separate diagram. All coverage starts Unknown pending evidence. PTC-X remains excluded from the active register.</x:v>
+      <x:c r="B23" s="9" t="inlineStr">
+        <x:is>
+          <x:t>CFG-001: VCU Rev9 component dimensions; nine solid-property candidate functions with SI units and working domains; portable source copies; dated nominal-ID, insulation and heater assumptions in evidence records. Physical installation and approval remain open.</x:t>
+        </x:is>
       </x:c>
       <x:c r="C23" s="9" t="str">
         <x:v>Describe changes since the preceding configuration and identify evidence or the request.</x:v>
@@ -1410,14 +1883,18 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Input variable and output units</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Output W/(m K) reported; confirm T convention against original fit</x:v>
+      <x:c r="C9" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT candidate: T in K; k W/(m*K). Original fit temperature convention not independently verified.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>MAT lines 38-40</x:v>
+      <x:c r="E9" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; Materials MAIN-INS</x:t>
+        </x:is>
       </x:c>
       <x:c r="F9" s="19"/>
       <x:c r="G9" s="19"/>
@@ -1433,14 +1910,18 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Source-supported domain</x:v>
       </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>Notes report 297-533 K; original data/domain unverified</x:v>
+      <x:c r="C10" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Original claimed k fit 297-533 K; user-authorized working extrapolation to 278.15 K (5 C), not product validation.</x:t>
+        </x:is>
       </x:c>
       <x:c r="D10" s="18" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="E10" s="18" t="str">
-        <x:v>MAT line 40</x:v>
+      <x:c r="E10" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C</x:t>
+        </x:is>
       </x:c>
       <x:c r="F10" s="19"/>
       <x:c r="G10" s="19"/>
@@ -1548,14 +2029,20 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Interpolation and outside-domain policy</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>Not selected</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>Proposed implementation record</x:v>
+      <x:c r="C15" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT candidate: evaluate polynomial within working domain; error outside. No approved release implied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT properties.conductivity</x:t>
+        </x:is>
       </x:c>
       <x:c r="F15" s="19"/>
       <x:c r="G15" s="19"/>
@@ -1594,14 +2081,20 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Check values, implementation and version</x:v>
       </x:c>
-      <x:c r="C17" s="18" t="str">
-        <x:v>Not implemented or independently checked</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="str">
-        <x:v>Proposed property tests</x:v>
+      <x:c r="C17" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT v3 implementation candidate retained; portable coefficient transcription checks in CFG-001 report. Original data comparison remains open.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; CFG-001 report</x:t>
+        </x:is>
       </x:c>
       <x:c r="F17" s="19"/>
       <x:c r="G17" s="19"/>
@@ -1644,7 +2137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
@@ -2216,17 +2709,23 @@
       <x:c r="H14" s="17" t="str">
         <x:v>Geometry map; Main swept loop</x:v>
       </x:c>
-      <x:c r="I14" s="17" t="str">
-        <x:v>Main CAD bore absent; notes report nominal 1.049 in (26.64 mm)</x:v>
+      <x:c r="I14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD main bore absent. GEO-008 retains 26.64 mm rounded nominal ID for provisional main piping; not a CAD-extracted bore or installed measurement. Local spool bores differ.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J14" s="17" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="str">
-        <x:v>DIA; MAT</x:v>
-      </x:c>
-      <x:c r="L14" s="17" t="str">
-        <x:v>Main swept loop row; VCU Piping lines 23-27</x:v>
+      <x:c r="K14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIA; VSEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Main swept loop; GEO-008 main nominal ID; CAD dimensions tab</x:t>
+        </x:is>
       </x:c>
       <x:c r="M14" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -2408,17 +2907,23 @@
       <x:c r="H18" s="17" t="str">
         <x:v>Geometry map; VCU insulation</x:v>
       </x:c>
-      <x:c r="I18" s="17" t="str">
-        <x:v>Main: fiberglass 5556K73; heater: calcium aluminum silicate 4057K14 reported</x:v>
+      <x:c r="I18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported fiberglass main insulation and calcium-aluminum-silicate heater strip. VINS v5 specifies regional candidates; product/installation evidence unresolved.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J18" s="17" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="str">
-        <x:v>MAT</x:v>
-      </x:c>
-      <x:c r="L18" s="17" t="str">
-        <x:v>Lines 29-44</x:v>
+      <x:c r="K18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>MAT; VINS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Materials; insulation.yaml regions; source copies in support/evidence/2026-10-16_CFG-001_vcu_references</x:t>
+        </x:is>
       </x:c>
       <x:c r="M18" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -2456,17 +2961,23 @@
       <x:c r="H19" s="17" t="str">
         <x:v>Geometry map; VCU insulation</x:v>
       </x:c>
-      <x:c r="I19" s="17" t="str">
-        <x:v>Most piping about 2 in; heater insulation 1/4 in reported</x:v>
+      <x:c r="I19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Approximate regional estimates: ordinary insulated pipe 50.8 mm fiberglass; heater 6.35 mm strip only. Top D-E is bare per GEO-008. Not measured thicknesses.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J19" s="17" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="str">
-        <x:v>MAT</x:v>
-      </x:c>
-      <x:c r="L19" s="17" t="str">
-        <x:v>Lines 29-44</x:v>
+      <x:c r="K19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VINS; VSEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>insulation.yaml regions.non_heater_main_pipe and heater_leg; GEO-008 top-leg qualification</x:t>
+        </x:is>
       </x:c>
       <x:c r="M19" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -2504,20 +3015,30 @@
       <x:c r="H20" s="17" t="str">
         <x:v>Method: facility and fluid configuration; geometry map</x:v>
       </x:c>
-      <x:c r="I20" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L20" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="str">
-        <x:v>Needs information</x:v>
+      <x:c r="I20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-008 reports whole top D-E uninsulated; all STCs contact bare pipe locally. Remaining transition endpoints unknown. Older full-loop coverage text is superseded.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; VINS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-008 User direction and interpretation; insulation.yaml coverage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N20" s="17" t="str">
         <x:v>Supply evidence and request review.</x:v>
@@ -2552,17 +3073,23 @@
       <x:c r="H21" s="17" t="str">
         <x:v>Geometry map; VCU Insulation</x:v>
       </x:c>
-      <x:c r="I21" s="17" t="str">
-        <x:v>Firm contact is explicitly an assumption in notes</x:v>
+      <x:c r="I21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Perfect thermal contact is a user-directed model assumption (VINS), not a surveyed contact condition. Actual supports, gaps and layers remain open.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J21" s="17" t="str">
         <x:v>Modeling assumption</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="str">
-        <x:v>HEAT</x:v>
-      </x:c>
-      <x:c r="L21" s="17" t="str">
-        <x:v>VCU Insulation lines 7-10</x:v>
+      <x:c r="K21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VINS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>insulation.yaml contact</x:t>
+        </x:is>
       </x:c>
       <x:c r="M21" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -3416,17 +3943,25 @@
       <x:c r="H39" s="17" t="str">
         <x:v>Geometry map; heater note; sheet 4</x:v>
       </x:c>
-      <x:c r="I39" s="17" t="str">
-        <x:v>Four clamps in CAD; notes report mat/band electrical heaters and intended 40-in coverage</x:v>
-      </x:c>
-      <x:c r="J39" s="17" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="str">
-        <x:v>HEAT; R9</x:v>
-      </x:c>
-      <x:c r="L39" s="17" t="str">
-        <x:v>HEAT lines 16-23; R9 sheet 4</x:v>
+      <x:c r="I39" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Electrical heater footprint remains unverified. GEO-008 assumes full projected H-A span 0-1346.496215 mm for modeling only; mechanical clamps do not establish active heating.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J39" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K39" s="17" t="inlineStr">
+        <x:is>
+          <x:t>HEAT; VSEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L39" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-008 lower-leg assumption; original Active heater baseline remains null</x:t>
+        </x:is>
       </x:c>
       <x:c r="M39" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -4136,17 +4671,25 @@
       <x:c r="H54" s="17" t="str">
         <x:v>Sheet 8 qualifications; model stages</x:v>
       </x:c>
-      <x:c r="I54" s="17" t="str">
-        <x:v>Heater overlap/offset and G-H path require an explicit interpretation</x:v>
-      </x:c>
-      <x:c r="J54" s="17" t="str">
-        <x:v>CAD-derived</x:v>
-      </x:c>
-      <x:c r="K54" s="17" t="str">
-        <x:v>R9</x:v>
-      </x:c>
-      <x:c r="L54" s="17" t="str">
-        <x:v>Sheets 2, 8</x:v>
+      <x:c r="I54" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Rev9 selected as provisional working geometry; main nominal ID 26.64 mm is separate from CAD null. H-A projected union is not an exact connected centerline; G-H reconstructed spline remains qualified.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J54" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K54" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; SEG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L54" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-008 Why H-A has a qualification; Geometry notes; CAD dimensions tab</x:t>
+        </x:is>
       </x:c>
       <x:c r="M54" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -4376,20 +4919,30 @@
       <x:c r="H59" s="17" t="str">
         <x:v>Duty definitions; VCU electrical adaptation</x:v>
       </x:c>
-      <x:c r="I59" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J59" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K59" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L59" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M59" s="17" t="str">
-        <x:v>Needs information</x:v>
+      <x:c r="I59" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-008 assumes uniform extent over H-A projected span 1346.496215 mm. Real electrical power, spatial distribution, efficiency and heater/structure storage remain unresolved.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J59" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K59" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; HEAT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L59" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-008 lower-leg modeling assumption; Thermal spans keeps installed footprint unknown</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M59" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N59" s="17" t="str">
         <x:v>Specify spatial source, meter boundary, external losses and storage without double counting.</x:v>
@@ -4568,17 +5121,23 @@
       <x:c r="H63" s="17" t="str">
         <x:v>Definitions: fixed property reference</x:v>
       </x:c>
-      <x:c r="I63" s="17" t="str">
-        <x:v>Reported 316L and insulation products; exact fluid formulation unresolved</x:v>
+      <x:c r="I63" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported 316L pipe, fiberglass candidate and calcium-aluminum-silicate strip; VMAT explicitly marks all three calibration-ineligible and unverified against installed products. Fluid formulation remains unresolved.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J63" s="17" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K63" s="17" t="str">
-        <x:v>MAT</x:v>
-      </x:c>
-      <x:c r="L63" s="17" t="str">
-        <x:v>VCU section lines 17-44</x:v>
+      <x:c r="K63" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; MAT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L63" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT materials.*.provenance and calibration_eligible; Materials tab</x:t>
+        </x:is>
       </x:c>
       <x:c r="M63" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -4616,17 +5175,23 @@
       <x:c r="H64" s="17" t="str">
         <x:v>Definitions and Conventions</x:v>
       </x:c>
-      <x:c r="I64" s="17" t="str">
-        <x:v>Insulation k(T) candidate exists in notes; no correlation approved</x:v>
+      <x:c r="I64" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Nine explicit solid rho/cp/k functions transcribed from VMAT v3. Original derivations and installed-product source data remain unverified. No fluid functions imported.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J64" s="17" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K64" s="17" t="str">
-        <x:v>MAT; STEEL; PG</x:v>
-      </x:c>
-      <x:c r="L64" s="17" t="str">
-        <x:v>MAT lines 35-40; STEEL Suggested you use; PG notes</x:v>
+      <x:c r="K64" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L64" s="17" t="inlineStr">
+        <x:is>
+          <x:t>vcu_candidate_materials_v3.yaml materials.*.properties; Materials equations</x:t>
+        </x:is>
       </x:c>
       <x:c r="M64" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -4664,20 +5229,30 @@
       <x:c r="H65" s="17" t="str">
         <x:v>Definitions: property reference</x:v>
       </x:c>
-      <x:c r="I65" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J65" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K65" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L65" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M65" s="17" t="str">
-        <x:v>Needs information</x:v>
+      <x:c r="I65" s="17" t="inlineStr">
+        <x:is>
+          <x:t>All imported solid functions take T in K; rho kg/m^3, cp J/(kg*K), k W/(m*K). Prop-30 mass fraction 0.30 is reported; formulation verification pending.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J65" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K65" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; PG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L65" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT properties units/coefficient_order; Fluids tab</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M65" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N65" s="17" t="str">
         <x:v>Record K versus deg C, pressure units, mass/volume fraction and output units for each function.</x:v>
@@ -4712,17 +5287,25 @@
       <x:c r="H66" s="17" t="str">
         <x:v>Property reference; temperature/condensation applicability</x:v>
       </x:c>
-      <x:c r="I66" s="17" t="str">
-        <x:v>Insulation fit is reported valid 297-533 K; not an experiment operating range</x:v>
-      </x:c>
-      <x:c r="J66" s="17" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="K66" s="17" t="str">
-        <x:v>MAT</x:v>
-      </x:c>
-      <x:c r="L66" s="17" t="str">
-        <x:v>Lines 38-40</x:v>
+      <x:c r="I66" s="17" t="inlineStr">
+        <x:is>
+          <x:t>User-authorized working intervals: pipe 278.15-813 K; fiberglass 278.15-533 K; heater strip 278.15-1089 K. ADR-0033 extends all nine functions to 5 C; extrapolation is not product validation or an operating limit.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J66" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K66" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L66" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT valid_temperature_K; ADR-0033 Decision and authority</x:t>
+        </x:is>
       </x:c>
       <x:c r="M66" s="17" t="str">
         <x:v>Needs review</x:v>
@@ -4760,20 +5343,30 @@
       <x:c r="H67" s="17" t="str">
         <x:v>Proposed implementation control</x:v>
       </x:c>
-      <x:c r="I67" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J67" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K67" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L67" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M67" s="17" t="str">
-        <x:v>Needs information</x:v>
+      <x:c r="I67" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT polynomial functions use ascending powers of T in K; density/cp constants as specified; all nine functions specify out_of_range: error. No fluid interpolation policy supplied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J67" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K67" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L67" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT materials.*.properties model/coefficient_order/out_of_range</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M67" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N67" s="17" t="str">
         <x:v>Specify interpolation; reject/flag extrapolation explicitly rather than silently clipping.</x:v>
@@ -4856,20 +5449,30 @@
       <x:c r="H69" s="17" t="str">
         <x:v>Requested material-property justification</x:v>
       </x:c>
-      <x:c r="I69" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J69" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K69" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L69" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M69" s="17" t="str">
-        <x:v>Needs information</x:v>
+      <x:c r="I69" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Candidate working functions supplied by user; ADR-0033 authorizes low-temperature extrapolation. Reported independent pipe comparison has no retained comparison table; package transfer does not establish independent validation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J69" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K69" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L69" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT provenance; ADR-0033 Evidence and limits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M69" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N69" s="17" t="str">
         <x:v>Compare candidate sources and explain selection or any deliberate mixed-source set.</x:v>
@@ -5559,7 +6162,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe3645e732ce4448"/>
+    <x:tablePart r:id="Rfe3645e732ce4448"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6508,7 +7111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
@@ -6856,10 +7459,118 @@
         <x:v>Assistant-proposed documentation field/convention, not an approved physical fact.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>2026-10-07 v3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>materials.*.properties; provenance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Nine user-supplied solid-property candidates; not product verified; calibration-ineligible. Coverage wording in older provenance is superseded by VSEL.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>V5C</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/ADR-0033-vcu-solid-properties-5c.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>2026-10-07 accepted working-range decision</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Decision and authority; Evidence and limits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>User authorizes working extrapolation to 5 C, not source/product validation or an operating limit.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>2026-10-14 provisional working selection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>User direction and interpretation; Why H-A has a qualification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Dated working geometry/installation choices; historical run dates, tips and electrical footprint unresolved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VINS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>v5 2026-10-07, amended by VSEL for Rev9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>coverage; contact; regions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Regional thickness estimates/contact assumption; exact transitions and installed construction unverified. VSEL is later controlling top-leg evidence.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd789b6a13c34804"/>
+    <x:tablePart r:id="Rbd789b6a13c34804"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7042,8 +7753,16 @@
       <x:c r="G6" s="33" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="H6" s="33"/>
-      <x:c r="I6" s="33"/>
+      <x:c r="H6" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml / non_heater_main_pipe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I6" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported approximate 50.8 mm fiberglass candidate; exact transitions/gaps and bare STC contacts unresolved. Whole-region coverage remains Unknown.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="32" t="str">
@@ -7076,16 +7795,28 @@
       <x:c r="C8" s="32" t="str">
         <x:v>Segment start to Complete jacket start</x:v>
       </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D8" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Bare</x:t>
+        </x:is>
       </x:c>
       <x:c r="E8" s="33"/>
       <x:c r="F8" s="34"/>
-      <x:c r="G8" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-      <x:c r="I8" s="33"/>
+      <x:c r="G8" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md / whole top D-E leg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" s="33" t="inlineStr">
+        <x:is>
+          <x:t>October 14 user-reported working installation; not independently surveyed. Water jacket remains present; Bare does not imply room-air exposure beneath jacket.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="32" t="str">
@@ -7097,17 +7828,27 @@
       <x:c r="C9" s="32" t="str">
         <x:v>Complete jacket start to Complete jacket end</x:v>
       </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D9" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Bare</x:t>
+        </x:is>
       </x:c>
       <x:c r="E9" s="33"/>
       <x:c r="F9" s="34"/>
-      <x:c r="G9" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-      <x:c r="I9" s="33" t="str">
-        <x:v>Identify the insulated surface, especially jacket exterior versus pipe.</x:v>
+      <x:c r="G9" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md / whole top D-E leg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" s="33" t="inlineStr">
+        <x:is>
+          <x:t>October 14 user-reported working installation; not independently surveyed. Water jacket remains present; Bare does not imply room-air exposure beneath jacket.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -7120,16 +7861,28 @@
       <x:c r="C10" s="32" t="str">
         <x:v>Complete jacket end to segment end</x:v>
       </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D10" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Bare</x:t>
+        </x:is>
       </x:c>
       <x:c r="E10" s="33"/>
       <x:c r="F10" s="34"/>
-      <x:c r="G10" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
-      <x:c r="I10" s="33"/>
+      <x:c r="G10" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md / whole top D-E leg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" s="33" t="inlineStr">
+        <x:is>
+          <x:t>October 14 user-reported working installation; not independently surveyed. Water jacket remains present; Bare does not imply room-air exposure beneath jacket.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="32" t="str">
@@ -7170,8 +7923,16 @@
       <x:c r="G12" s="33" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="H12" s="33"/>
-      <x:c r="I12" s="33"/>
+      <x:c r="H12" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml / non_heater_main_pipe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported approximate 50.8 mm fiberglass candidate; exact transitions/gaps and bare STC contacts unresolved. Whole-region coverage remains Unknown.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="32" t="str">
@@ -7212,8 +7973,16 @@
       <x:c r="G14" s="33" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="H14" s="33"/>
-      <x:c r="I14" s="33"/>
+      <x:c r="H14" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml / heater_leg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I14" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported approximate 6.35 mm calcium-aluminum-silicate strip only; exact coverage and installed stack unverified. Whole-region coverage remains Unknown.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="32" t="str">
@@ -7422,8 +8191,10 @@
       <x:c r="M6" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N6" s="8" t="str">
-        <x:v>Continuous straight axis</x:v>
+      <x:c r="N6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Continuous straight axis; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
@@ -7458,8 +8229,10 @@
       <x:c r="M7" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N7" s="8" t="str">
-        <x:v>Exact analytical torus centerline arc</x:v>
+      <x:c r="N7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Exact analytical torus centerline arc; CAD torus radius 57.150000 mm, angle 100.800000 deg, arc 100.543531 mm. Diagram connector remains schematic.; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
@@ -7494,8 +8267,10 @@
       <x:c r="M8" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N8" s="8" t="str">
-        <x:v>Continuous straight axis</x:v>
+      <x:c r="N8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Continuous straight axis; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
@@ -7530,8 +8305,10 @@
       <x:c r="M9" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N9" s="8" t="str">
-        <x:v>Exact analytical torus centerline arc</x:v>
+      <x:c r="N9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Exact analytical torus centerline arc; CAD torus radius 57.150000 mm, angle 79.200000 deg, arc 78.998489 mm. Diagram connector remains schematic.; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
@@ -7566,8 +8343,10 @@
       <x:c r="M10" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N10" s="8" t="str">
-        <x:v>Continuous straight axis</x:v>
+      <x:c r="N10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Continuous straight axis; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
@@ -7602,8 +8381,10 @@
       <x:c r="M11" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N11" s="8" t="str">
-        <x:v>Endpoint chord exact; recovered spline spine qualified by endpoint residuals</x:v>
+      <x:c r="N11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Endpoint chord exact; recovered spline spine qualified by endpoint residuals; recovered spine 98.265651493 mm is qualified; exact centerline length remains unknown.; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
@@ -7638,8 +8419,10 @@
       <x:c r="M12" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N12" s="8" t="str">
-        <x:v>Projected endpoint-to-endpoint axial span; overlapping offset pieces retained, no healed centerline</x:v>
+      <x:c r="N12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Projected endpoint-to-endpoint axial span; overlapping offset pieces retained, no healed centerline; axis sum 1353.698559747 mm, projected overlap 7.202344895 mm, transverse offset 0.151551091 mm. VSEL full-span heating is a modeling assumption; installed footprint unknown.; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
@@ -7674,8 +8457,10 @@
       <x:c r="M13" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 1-3</x:v>
       </x:c>
-      <x:c r="N13" s="8" t="str">
-        <x:v>Exact analytical torus centerline arc</x:v>
+      <x:c r="N13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Exact analytical torus centerline arc; CAD torus radius 57.150000 mm, angle 79.200000 deg, arc 78.998489 mm. Diagram connector remains schematic.; portable SEG CSV in support/evidence/2026-10-16_CFG-001_vcu_references/VCU_Rev9_Segments.csv.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9484,19 +10269,39 @@
       <x:c r="C6" s="8" t="str">
         <x:v>rho, cp, k</x:v>
       </x:c>
-      <x:c r="D6" s="8"/>
-      <x:c r="E6" s="8"/>
-      <x:c r="F6" s="8"/>
-      <x:c r="G6" s="8"/>
+      <x:c r="D6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>rho(T) = (8066.715) + (-0.398373)*T; cp(T) = (279.256) + (0.732165)*T + (-0.000459146)*T^2; k(T) = (9.248) + (0.01571)*T</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>T in kelvin (K)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>rho: kg/m^3; cp: J/(kg*K); k: W/(m*K)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Working use only: 278.15-813 K; lower extension authorized 2026-10-07, not product validation. Pressure domain not supplied.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="H6" s="8"/>
-      <x:c r="I6" s="8" t="str">
-        <x:v>Reconcile candidate correlations and installed specification.</x:v>
+      <x:c r="I6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J6" s="8" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K6" s="8" t="str">
-        <x:v>1.2 Main Material Props.md; 1.2.2 Steel Pipe Properties.md</x:v>
+      <x:c r="K6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_pipe_316l_user_candidate_v1.properties</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
@@ -9509,19 +10314,39 @@
       <x:c r="C7" s="8" t="str">
         <x:v>rho, cp, k</x:v>
       </x:c>
-      <x:c r="D7" s="8"/>
-      <x:c r="E7" s="8"/>
-      <x:c r="F7" s="8"/>
-      <x:c r="G7" s="8"/>
+      <x:c r="D7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>rho(T) = 72.08; cp(T) = 840.0; k(T) = (0.0678938) + (-0.000289613)*T + (5.84142e-07)*T^2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>T in kelvin (K)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>rho: kg/m^3; cp: J/(kg*K); k: W/(m*K)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Working use only: 278.15-533 K; lower extension authorized 2026-10-07, not product validation. Pressure domain not supplied.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="H7" s="8"/>
-      <x:c r="I7" s="8" t="str">
-        <x:v>Confirm installed layers and original product evidence.</x:v>
+      <x:c r="I7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error. Approximate 50.8 mm thickness is a provisional regional estimate, not a measurement; old library coverage wording is superseded by GEO-008.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J7" s="8" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K7" s="8" t="str">
-        <x:v>1.2 Main Material Props.md</x:v>
+      <x:c r="K7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_main_fiberglass_user_candidate_v1.properties</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
@@ -9534,19 +10359,39 @@
       <x:c r="C8" s="8" t="str">
         <x:v>rho, cp, k</x:v>
       </x:c>
-      <x:c r="D8" s="8"/>
-      <x:c r="E8" s="8"/>
-      <x:c r="F8" s="8"/>
-      <x:c r="G8" s="8"/>
+      <x:c r="D8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>rho(T) = 560.65; cp(T) = (709.85) + (0.3075)*T; k(T) = (0.101729) + (-0.000201327)*T + (3.21455e-07)*T^2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>T in kelvin (K)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>rho: kg/m^3; cp: J/(kg*K); k: W/(m*K)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Working use only: 278.15-1089 K; lower extension authorized 2026-10-07, not product validation. Pressure domain not supplied.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="H8" s="8"/>
-      <x:c r="I8" s="8" t="str">
-        <x:v>Confirm installed stack and contacts.</x:v>
+      <x:c r="I8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error. Approximate 6.35 mm strip only on heater leg; installed layer order and contacts unverified.</x:t>
+        </x:is>
       </x:c>
       <x:c r="J8" s="8" t="str">
         <x:v>Reported</x:v>
       </x:c>
-      <x:c r="K8" s="8" t="str">
-        <x:v>1.2 Main Material Props.md</x:v>
+      <x:c r="K8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_heater_cas_strip_user_candidate_v1.properties</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
@@ -9860,6 +10705,90 @@
       <x:c r="G14" s="8"/>
       <x:c r="H14" s="8" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Main nominal bore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>CAD bore absent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reference working nominal ID 26.64 mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Nominal ID 26.64 mm candidate; local restrictions need explicit treatment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; DIA. Rounded nominal selection; not a CAD bore or installed measurement. Geometry ID cells remain null.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Actual bore and local spool restrictions unresolved.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Heater spatial extent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Electrical footprint unverified</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reference assumption: H-A 0 to 1346.496215 mm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Same projected-span candidate; connected geometry and heat source require review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL. Full lower-leg heating assumption only; active baseline spans remain null.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Electrical power split, storage, losses and footprint unresolved.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -1032,7 +1032,7 @@
       </x:c>
       <x:c r="B7" s="9" t="inlineStr">
         <x:is>
-          <x:t>VCU-REV9-DRAFT-004</x:t>
+          <x:t>VCU-REV9-DRAFT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" s="8" t="str">
@@ -1210,7 +1210,7 @@
       </x:c>
       <x:c r="B23" s="9" t="inlineStr">
         <x:is>
-          <x:t>CFG-001: VCU Rev9 component dimensions; nine solid-property candidate functions with SI units and working domains; portable source copies; dated nominal-ID, insulation and heater assumptions in evidence records. Physical installation and approval remain open.</x:t>
+          <x:t>GEO-009: entire covered top-left C-D and top-right E-F corners Insulated; LF-01 locally covered, per Andres Fierro 2026-10-16. Model regional insulation v6 and Rev9 working selection v2 agree. Other coverage, numerical geometry and historical evidence unchanged.</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" s="9" t="str">
@@ -3017,7 +3017,7 @@
       </x:c>
       <x:c r="I20" s="17" t="inlineStr">
         <x:is>
-          <x:t>GEO-008 reports whole top D-E uninsulated; all STCs contact bare pipe locally. Remaining transition endpoints unknown. Older full-loop coverage text is superseded.</x:t>
+          <x:t>User 2026-10-16: entire C-D/E-F upper corners insulated; LF-01 locally covered. Top D-E remains bare. Remaining vertical cutbacks and LF-01 coverage extent unknown.</x:t>
         </x:is>
       </x:c>
       <x:c r="J20" s="17" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </x:c>
       <x:c r="K20" s="17" t="inlineStr">
         <x:is>
-          <x:t>VSEL; VINS</x:t>
+          <x:t>VSEL; VTOP</x:t>
         </x:is>
       </x:c>
       <x:c r="L20" s="17" t="inlineStr">
         <x:is>
-          <x:t>GEO-008 User direction and interpretation; insulation.yaml coverage</x:t>
+          <x:t>VTOP direct user clarification; Insulation regions INS-02/06; Sensors LF-01; regional model v6</x:t>
         </x:is>
       </x:c>
       <x:c r="M20" s="17" t="inlineStr">
@@ -7567,6 +7567,33 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VTOP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_GEO-009_covered_top_corners/USER_CLARIFICATION.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Direct user clarification 2026-10-16; model regional v6 / Rev9 working v2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Whole C-D / E-F corners; LF-01 local exposure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported by user; no independent survey, optical extent, covered extent or historical run dates supplied.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
@@ -7774,16 +7801,28 @@
       <x:c r="C7" s="32" t="str">
         <x:v>Full schematic corner</x:v>
       </x:c>
-      <x:c r="D7" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D7" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
       </x:c>
       <x:c r="E7" s="33"/>
       <x:c r="F7" s="34"/>
-      <x:c r="G7" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H7" s="33"/>
-      <x:c r="I7" s="33"/>
+      <x:c r="G7" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_GEO-009_covered_top_corners/USER_CLARIFICATION.md / entire covered top-left C-D and top-right E-F corners</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Entire corner insulated per corrected Andres Fierro statement 2026-10-16. Installed product and thickness unmeasured; model fiberglass estimate remains provisional.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="32" t="str">
@@ -7894,16 +7933,28 @@
       <x:c r="C11" s="32" t="str">
         <x:v>Full schematic corner</x:v>
       </x:c>
-      <x:c r="D11" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D11" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
       </x:c>
       <x:c r="E11" s="33"/>
       <x:c r="F11" s="34"/>
-      <x:c r="G11" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H11" s="33"/>
-      <x:c r="I11" s="33"/>
+      <x:c r="G11" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_GEO-009_covered_top_corners/USER_CLARIFICATION.md / entire covered top-left C-D and top-right E-F corners</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Entire corner insulated per corrected Andres Fierro statement 2026-10-16. Installed product and thickness unmeasured; model fiberglass estimate remains provisional.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="32" t="str">
@@ -8748,8 +8799,10 @@
       <x:c r="K10" s="8" t="str">
         <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
       </x:c>
-      <x:c r="L10" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="L10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Actual sensing location and channel mapping unverified. User report 2026-10-16 (VTOP): LF-01 is covered locally. CAD mount reference lies on upcomer 61.113919 mm below C; covered extent, optical extent and DAQ mapping remain unknown.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">

--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -1032,7 +1032,7 @@
       </x:c>
       <x:c r="B7" s="9" t="inlineStr">
         <x:is>
-          <x:t>VCU-REV9-DRAFT-005</x:t>
+          <x:t>VCU-REV9-DRAFT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" s="8" t="str">
@@ -1210,7 +1210,7 @@
       </x:c>
       <x:c r="B23" s="9" t="inlineStr">
         <x:is>
-          <x:t>GEO-009: entire covered top-left C-D and top-right E-F corners Insulated; LF-01 locally covered, per Andres Fierro 2026-10-16. Model regional insulation v6 and Rev9 working selection v2 agree. Other coverage, numerical geometry and historical evidence unchanged.</x:t>
+          <x:t>GEO-010: all ten insulation regions synchronized: six ordinary-pipe fiberglass regions about 50.8 mm; heater ceramic strip only about 6.35 mm; three top D-E partitions Bare. Coverage Reported; thicknesses approximate estimates. LF-01 remains covered.</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" s="9" t="str">
@@ -2909,24 +2909,28 @@
       </x:c>
       <x:c r="I18" s="17" t="inlineStr">
         <x:is>
-          <x:t>Reported fiberglass main insulation and calcium-aluminum-silicate heater strip. VINS v5 specifies regional candidates; product/installation evidence unresolved.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" s="17" t="str">
-        <x:v>Reported</x:v>
+          <x:t>Ordinary main piping (upcomer/downcomer and four corners): fiberglass MAIN-INS; heater: calcium-aluminum-silicate HEATER-INS strip only, no additional fiberglass.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="K18" s="17" t="inlineStr">
         <x:is>
-          <x:t>MAT; VINS</x:t>
+          <x:t>VREG; VTOP</x:t>
         </x:is>
       </x:c>
       <x:c r="L18" s="17" t="inlineStr">
         <x:is>
-          <x:t>Materials; insulation.yaml regions; source copies in support/evidence/2026-10-16_CFG-001_vcu_references</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M18" s="17" t="str">
-        <x:v>Needs review</x:v>
+          <x:t>VREG regional YAML and ADR-0025/0026; VTOP corner/LF-01 correction; user reaffirmation 2026-10-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N18" s="17" t="str">
         <x:v>Which product and layers are installed on this exact segment?</x:v>
@@ -2963,24 +2967,28 @@
       </x:c>
       <x:c r="I19" s="17" t="inlineStr">
         <x:is>
-          <x:t>Approximate regional estimates: ordinary insulated pipe 50.8 mm fiberglass; heater 6.35 mm strip only. Top D-E is bare per GEO-008. Not measured thicknesses.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" s="17" t="str">
-        <x:v>Reported</x:v>
+          <x:t>Reported estimates: ordinary insulated regions 50.8 mm (2 in); heater strip 6.35 mm (1/4 in). Not installed thickness measurements.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="K19" s="17" t="inlineStr">
         <x:is>
-          <x:t>VINS; VSEL</x:t>
+          <x:t>VREG; VTOP</x:t>
         </x:is>
       </x:c>
       <x:c r="L19" s="17" t="inlineStr">
         <x:is>
-          <x:t>insulation.yaml regions.non_heater_main_pipe and heater_leg; GEO-008 top-leg qualification</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M19" s="17" t="str">
-        <x:v>Needs review</x:v>
+          <x:t>VREG regional YAML and ADR-0025/0026; VTOP corner/LF-01 correction; user reaffirmation 2026-10-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
       </x:c>
       <x:c r="N19" s="17" t="str">
         <x:v>Measure each layer; do not apply either value everywhere.</x:v>
@@ -3017,7 +3025,7 @@
       </x:c>
       <x:c r="I20" s="17" t="inlineStr">
         <x:is>
-          <x:t>User 2026-10-16: entire C-D/E-F upper corners insulated; LF-01 locally covered. Top D-E remains bare. Remaining vertical cutbacks and LF-01 coverage extent unknown.</x:t>
+          <x:t>Reported coverage known for all ten regions: upcomer/downcomer, four corners and heater insulated; pre-cooler/jacket/post-cooler D-E bare. LF-01 covered. Exact local contacts and transitions remain open.</x:t>
         </x:is>
       </x:c>
       <x:c r="J20" s="17" t="inlineStr">
@@ -3027,12 +3035,12 @@
       </x:c>
       <x:c r="K20" s="17" t="inlineStr">
         <x:is>
-          <x:t>VSEL; VTOP</x:t>
+          <x:t>VREG; VTOP</x:t>
         </x:is>
       </x:c>
       <x:c r="L20" s="17" t="inlineStr">
         <x:is>
-          <x:t>VTOP direct user clarification; Insulation regions INS-02/06; Sensors LF-01; regional model v6</x:t>
+          <x:t>VREG regional YAML and ADR-0025/0026; VTOP corner/LF-01 correction; user reaffirmation 2026-10-16</x:t>
         </x:is>
       </x:c>
       <x:c r="M20" s="17" t="inlineStr">
@@ -7594,6 +7602,33 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VREG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/README.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-010 2026-10-16; regional v7 / working v3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>region_assignments.json; insulation.yaml; ADR-0025/0026; USER_CONFIRMATION.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported coverage and approximate thickness estimates; product/fit validation, installed surveys and historical applicability remain separate.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
@@ -7772,22 +7807,32 @@
       <x:c r="C6" s="32" t="str">
         <x:v>Full segment</x:v>
       </x:c>
-      <x:c r="D6" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E6" s="33"/>
-      <x:c r="F6" s="34"/>
-      <x:c r="G6" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D6" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="33" t="inlineStr">
+        <x:is>
+          <x:t>MAIN-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="34">
+        <x:v>50.8</x:v>
+      </x:c>
+      <x:c r="G6" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="H6" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml / non_heater_main_pipe</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I6" s="33" t="inlineStr">
         <x:is>
-          <x:t>Reported approximate 50.8 mm fiberglass candidate; exact transitions/gaps and bare STC contacts unresolved. Whole-region coverage remains Unknown.</x:t>
+          <x:t>Reported ordinary main-pipe fiberglass assignment, approximately 2 in; regional model candidate, not installed product/thickness validation. Local STC contacts/transition details remain separate.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7806,8 +7851,14 @@
           <x:t>Insulated</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="33"/>
-      <x:c r="F7" s="34"/>
+      <x:c r="E7" s="33" t="inlineStr">
+        <x:is>
+          <x:t>MAIN-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="34">
+        <x:v>50.8</x:v>
+      </x:c>
       <x:c r="G7" s="33" t="inlineStr">
         <x:is>
           <x:t>Reported</x:t>
@@ -7815,12 +7866,12 @@
       </x:c>
       <x:c r="H7" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_GEO-009_covered_top_corners/USER_CLARIFICATION.md / entire covered top-left C-D and top-right E-F corners</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I7" s="33" t="inlineStr">
         <x:is>
-          <x:t>Entire corner insulated per corrected Andres Fierro statement 2026-10-16. Installed product and thickness unmeasured; model fiberglass estimate remains provisional.</x:t>
+          <x:t>Reported ordinary main-pipe fiberglass assignment, approximately 2 in; regional model candidate, not installed product/thickness validation. Local STC contacts/transition details remain separate.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7848,12 +7899,12 @@
       </x:c>
       <x:c r="H8" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md / whole top D-E leg</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I8" s="33" t="inlineStr">
         <x:is>
-          <x:t>October 14 user-reported working installation; not independently surveyed. Water jacket remains present; Bare does not imply room-air exposure beneath jacket.</x:t>
+          <x:t>Reported straight top D-E bare, GEO-008 retained; water jacket remains present.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7881,12 +7932,12 @@
       </x:c>
       <x:c r="H9" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md / whole top D-E leg</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I9" s="33" t="inlineStr">
         <x:is>
-          <x:t>October 14 user-reported working installation; not independently surveyed. Water jacket remains present; Bare does not imply room-air exposure beneath jacket.</x:t>
+          <x:t>Reported straight top D-E bare, GEO-008 retained; water jacket remains present.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7914,12 +7965,12 @@
       </x:c>
       <x:c r="H10" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/2026-10-14_GEO-008_rev9_working_selection.md / whole top D-E leg</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I10" s="33" t="inlineStr">
         <x:is>
-          <x:t>October 14 user-reported working installation; not independently surveyed. Water jacket remains present; Bare does not imply room-air exposure beneath jacket.</x:t>
+          <x:t>Reported straight top D-E bare, GEO-008 retained; water jacket remains present.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7938,8 +7989,14 @@
           <x:t>Insulated</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="33"/>
-      <x:c r="F11" s="34"/>
+      <x:c r="E11" s="33" t="inlineStr">
+        <x:is>
+          <x:t>MAIN-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="34">
+        <x:v>50.8</x:v>
+      </x:c>
       <x:c r="G11" s="33" t="inlineStr">
         <x:is>
           <x:t>Reported</x:t>
@@ -7947,12 +8004,12 @@
       </x:c>
       <x:c r="H11" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_GEO-009_covered_top_corners/USER_CLARIFICATION.md / entire covered top-left C-D and top-right E-F corners</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I11" s="33" t="inlineStr">
         <x:is>
-          <x:t>Entire corner insulated per corrected Andres Fierro statement 2026-10-16. Installed product and thickness unmeasured; model fiberglass estimate remains provisional.</x:t>
+          <x:t>Reported ordinary main-pipe fiberglass assignment, approximately 2 in; regional model candidate, not installed product/thickness validation. Local STC contacts/transition details remain separate.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7966,22 +8023,32 @@
       <x:c r="C12" s="32" t="str">
         <x:v>Full segment</x:v>
       </x:c>
-      <x:c r="D12" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E12" s="33"/>
-      <x:c r="F12" s="34"/>
-      <x:c r="G12" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D12" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="33" t="inlineStr">
+        <x:is>
+          <x:t>MAIN-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="34">
+        <x:v>50.8</x:v>
+      </x:c>
+      <x:c r="G12" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="H12" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml / non_heater_main_pipe</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I12" s="33" t="inlineStr">
         <x:is>
-          <x:t>Reported approximate 50.8 mm fiberglass candidate; exact transitions/gaps and bare STC contacts unresolved. Whole-region coverage remains Unknown.</x:t>
+          <x:t>Reported ordinary main-pipe fiberglass assignment, approximately 2 in; regional model candidate, not installed product/thickness validation. Local STC contacts/transition details remain separate.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7995,16 +8062,34 @@
       <x:c r="C13" s="32" t="str">
         <x:v>Full schematic corner</x:v>
       </x:c>
-      <x:c r="D13" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E13" s="33"/>
-      <x:c r="F13" s="34"/>
-      <x:c r="G13" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H13" s="33"/>
-      <x:c r="I13" s="33"/>
+      <x:c r="D13" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="33" t="inlineStr">
+        <x:is>
+          <x:t>MAIN-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="34">
+        <x:v>50.8</x:v>
+      </x:c>
+      <x:c r="G13" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported ordinary main-pipe fiberglass assignment, approximately 2 in; regional model candidate, not installed product/thickness validation. Local STC contacts/transition details remain separate.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="32" t="str">
@@ -8016,22 +8101,32 @@
       <x:c r="C14" s="32" t="str">
         <x:v>Full segment</x:v>
       </x:c>
-      <x:c r="D14" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E14" s="33"/>
-      <x:c r="F14" s="34"/>
-      <x:c r="G14" s="33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="D14" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="33" t="inlineStr">
+        <x:is>
+          <x:t>HEATER-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="34">
+        <x:v>6.35</x:v>
+      </x:c>
+      <x:c r="G14" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="H14" s="33" t="inlineStr">
         <x:is>
-          <x:t>support/evidence/2026-10-16_CFG-001_vcu_references/insulation.yaml / heater_leg</x:t>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
         </x:is>
       </x:c>
       <x:c r="I14" s="33" t="inlineStr">
         <x:is>
-          <x:t>Reported approximate 6.35 mm calcium-aluminum-silicate strip only; exact coverage and installed stack unverified. Whole-region coverage remains Unknown.</x:t>
+          <x:t>Reported heater insulation: approximately 1/4 in calcium-aluminum-silicate ceramic-fiber strip only; no extra fiberglass. Thickness is an estimate, not measured.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8045,16 +8140,34 @@
       <x:c r="C15" s="32" t="str">
         <x:v>Full schematic corner</x:v>
       </x:c>
-      <x:c r="D15" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E15" s="33"/>
-      <x:c r="F15" s="34"/>
-      <x:c r="G15" s="33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="H15" s="33"/>
-      <x:c r="I15" s="33"/>
+      <x:c r="D15" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Insulated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="33" t="inlineStr">
+        <x:is>
+          <x:t>MAIN-INS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="34">
+        <x:v>50.8</x:v>
+      </x:c>
+      <x:c r="G15" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" s="33" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_GEO-010_regional_insulation_sync/insulation.yaml / regions; VREG; VCU-007/008 and GEO-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I15" s="33" t="inlineStr">
+        <x:is>
+          <x:t>Reported ordinary main-pipe fiberglass assignment, approximately 2 in; regional model candidate, not installed product/thickness validation. Local STC contacts/transition details remain separate.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10390,7 +10503,7 @@
       <x:c r="H7" s="8"/>
       <x:c r="I7" s="8" t="inlineStr">
         <x:is>
-          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error. Approximate 50.8 mm thickness is a provisional regional estimate, not a measurement; old library coverage wording is superseded by GEO-008.</x:t>
+          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error. Approximate 50.8 mm thickness is a provisional regional estimate, not a measurement; old library coverage wording is superseded by GEO-008. Assigned to upcomer, downcomer and all four corners; approximately 50.8 mm fiberglass. Reported assignment; exact product and thickness remain unverified.</x:t>
         </x:is>
       </x:c>
       <x:c r="J7" s="8" t="str">
@@ -10398,7 +10511,7 @@
       </x:c>
       <x:c r="K7" s="8" t="inlineStr">
         <x:is>
-          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_main_fiberglass_user_candidate_v1.properties</x:t>
+          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_main_fiberglass_user_candidate_v1.properties; VREG</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10435,7 +10548,7 @@
       <x:c r="H8" s="8"/>
       <x:c r="I8" s="8" t="inlineStr">
         <x:is>
-          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error. Approximate 6.35 mm strip only on heater leg; installed layer order and contacts unverified.</x:t>
+          <x:t>Reported user-supplied candidate; calibration_eligible=false. No original fit derivation, installed-product verification or uncertainty supplied. Below original lower bounds (pipe/strip 293 K, fiberglass k 297 K) is user-authorized extrapolation per ADR-0033; not a source-validated range. Outside working range: error. Approximate 6.35 mm strip only on heater leg; installed layer order and contacts unverified. Assigned to straight heater only; approximately 6.35 mm ceramic strip; no extra fiberglass. Reported assignment; exact product and thickness remain unverified.</x:t>
         </x:is>
       </x:c>
       <x:c r="J8" s="8" t="str">
@@ -10443,7 +10556,7 @@
       </x:c>
       <x:c r="K8" s="8" t="inlineStr">
         <x:is>
-          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_heater_cas_strip_user_candidate_v1.properties</x:t>
+          <x:t>VMAT; V5C; support/evidence/2026-10-16_CFG-001_vcu_references/vcu_candidate_materials_v3.yaml / materials.vcu_heater_cas_strip_user_candidate_v1.properties; VREG</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -11114,14 +11227,20 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Insulation product and layer order</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Most piping: fiberglass, reported 5556K73</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>MAT lines 29-35</x:v>
+      <x:c r="C13" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported fiberglass MAIN-INS on upcomer; heater uses distinct ceramic strip only.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VREG; user reaffirmation 2026-10-16</x:t>
+        </x:is>
       </x:c>
       <x:c r="F13" s="19"/>
       <x:c r="G13" s="19"/>
@@ -11137,14 +11256,20 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Thickness of each layer (mm)</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="str">
-        <x:v>About 2 in for most main piping; this segment unverified</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="E14" s="18" t="str">
-        <x:v>MAT lines 29-35</x:v>
+      <x:c r="C14" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Upcomer: reported approximate 50.8 mm fiberglass; estimate, not measurement.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VREG; user reaffirmation 2026-10-16</x:t>
+        </x:is>
       </x:c>
       <x:c r="F14" s="19"/>
       <x:c r="G14" s="19"/>
@@ -11160,14 +11285,20 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Coverage, gaps and condition</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>Unknown for this exact segment</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>P0 geometry/configuration request</x:v>
+      <x:c r="C15" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Upcomer insulated per documented assignment and user reaffirmation; exact gaps/condition unmeasured.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VREG; user reaffirmation 2026-10-16</x:t>
+        </x:is>
       </x:c>
       <x:c r="F15" s="19"/>
       <x:c r="G15" s="19"/>

--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -19,6 +19,8 @@
     <x:sheet name="Sources" sheetId="15" r:id="R598c4ac295604744"/>
     <x:sheet name="Insulation regions" sheetId="16" r:id="R0557123f889541bd"/>
     <x:sheet name="CAD dimensions" sheetId="17" r:id="rIdCFG001Dimensions"/>
+    <x:sheet name="Native channels" sheetId="18" r:id="rIdCFG002_18"/>
+    <x:sheet name="Current knowledge" sheetId="19" r:id="rIdCFG002_19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,6 +973,1420 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/cfg002_18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="95" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="11" t="inlineStr">
+        <x:is>
+          <x:t>VCU working native-channel register</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="12" t="inlineStr">
+        <x:is>
+          <x:t>20-channel core inventory; user-selected working bindings, not calibration or historical installation certification.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="11"/>
+      <x:c r="C2" s="11"/>
+      <x:c r="D2" s="11"/>
+      <x:c r="E2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="13" t="inlineStr">
+        <x:is>
+          <x:t>Sources and limitations remain explicit. Blank measured values mean unknown; no package approval implied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="11"/>
+      <x:c r="C3" s="11"/>
+      <x:c r="D3" s="11"/>
+      <x:c r="E3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="11"/>
+      <x:c r="B4" s="11"/>
+      <x:c r="C4" s="11"/>
+      <x:c r="D4" s="11"/>
+      <x:c r="E4" s="11"/>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
+      <x:c r="A5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Native channel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Reference / domain</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Working role / operator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Basis / source</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Limits / next evidence</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="145" customHeight="1">
+      <x:c r="A6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-02 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="145" customHeight="1">
+      <x:c r="A7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-03 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="145" customHeight="1">
+      <x:c r="A8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-04 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="145" customHeight="1">
+      <x:c r="A9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-05 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="145" customHeight="1">
+      <x:c r="A10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-06 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="145" customHeight="1">
+      <x:c r="A11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC-01 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Primary fluid; centerline observation assumed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK / ASM-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="145" customHeight="1">
+      <x:c r="A12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-07 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="145" customHeight="1">
+      <x:c r="A13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC-03 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Primary fluid; centerline observation assumed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK / ASM-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="145" customHeight="1">
+      <x:c r="A14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-08 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="145" customHeight="1">
+      <x:c r="A15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-09 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="145" customHeight="1">
+      <x:c r="A16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-10 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="145" customHeight="1">
+      <x:c r="A17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-11 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="145" customHeight="1">
+      <x:c r="A18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC-04 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Primary fluid; centerline observation assumed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK / ASM-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="145" customHeight="1">
+      <x:c r="A19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-12 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="145" customHeight="1">
+      <x:c r="A20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC-02 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Primary fluid; centerline observation assumed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK / ASM-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="145" customHeight="1">
+      <x:c r="A21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC-01 / main_loop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface; local bare contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="145" customHeight="1">
+      <x:c r="A22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>JTC-A / jacket_port</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>jacket outlet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="145" customHeight="1">
+      <x:c r="A23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>JTC-B / jacket_port</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>jacket inlet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working binding, 2026-10-14. CAD reference is not sensing junction; calibration and historical applicability unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="145" customHeight="1">
+      <x:c r="A24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Amb</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No accepted XYZ / auxiliary</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Room ambient temperature reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>XWALK; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Native name and candidate role; exact sensor placement, medium, calibration and run-specific use need confirmation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="145" customHeight="1">
+      <x:c r="A25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Tank</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No accepted XYZ / auxiliary</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Tank / secondary-boundary temperature reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>XWALK; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Native name and candidate role; exact sensor placement, medium, calibration and run-specific use need confirmation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="Rbd789b6a13c34804"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/cfg002_19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="95" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Current VCU understanding and evidence limits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="12" t="inlineStr">
+        <x:is>
+          <x:t>CFG-002 reconciliation 2026-10-16; reported, CAD-derived and assumed information remains distinct from verification.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="11"/>
+      <x:c r="C2" s="11"/>
+      <x:c r="D2" s="11"/>
+      <x:c r="E2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="13" t="inlineStr">
+        <x:is>
+          <x:t>Sources and limitations remain explicit. Blank measured values mean unknown; no package approval implied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="11"/>
+      <x:c r="C3" s="11"/>
+      <x:c r="D3" s="11"/>
+      <x:c r="E3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="11"/>
+      <x:c r="B4" s="11"/>
+      <x:c r="C4" s="11"/>
+      <x:c r="D4" s="11"/>
+      <x:c r="E4" s="11"/>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
+      <x:c r="A5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Record ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Topic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Current understanding</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Basis / source</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="16" t="inlineStr">
+        <x:is>
+          <x:t>Limits / next evidence</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="145" customHeight="1">
+      <x:c r="A6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Facility and configuration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VCU only; Rev9 documentation DRAFT-007. Current geometry working v3, insulation v7, solid materials v3.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>WORK; CURRENT; VMAT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Draft, not an installed release or model-ready input; ACU evidence does not qualify VCU.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="145" customHeight="1">
+      <x:c r="A7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Coordinates and lengths</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>B origin; x=B_CAD_Z-CAD_Z, y=CAD_Y-B_CAD_Y, n=CAD_X-B_CAD_X. Traverse B-C-D-E-F-G-H-A-B.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; Geometry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>A-H are axis endpoints, not virtual corners; lengths/projected spans and bend arcs have different bases.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="145" customHeight="1">
+      <x:c r="A8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Gravity and inclination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working gravity (0,-1,0); straight inclined axes about 10.8 deg; heater chord about 10.79355 deg.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Installed gravity survey absent; keep n and do not conflate circumferential angle with inclination.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="145" customHeight="1">
+      <x:c r="A9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Heater and lower-right geometry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>H-A projected union 1346.4962148518246 mm; pieces overlap 7.202344894878479 mm and are offset 0.1515510905213091 mm. G-H is reconstructed spine.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; CAD dimensions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No exact connected hydraulic centerline or silent healing.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="145" customHeight="1">
+      <x:c r="A10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K05</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Pipe dimensions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Main OD 33.401 mm CAD-derived. Working main ID 26.64 mm rounded nominal, separate from unknown CAD bore; component-specific bores in CAD dimensions.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; DIA; Model choices</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Main Geometry ID remains blank; do not fill from local spools.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="145" customHeight="1">
+      <x:c r="A11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K06</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Insulation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Six ordinary-pipe regions fiberglass about 50.8 mm; straight heater ceramic strip only about 6.35 mm; three straight D-E regions bare. Both upper corners insulated; LF-01 locally covered.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CURRENT; VREG; VTOP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported thickness estimates, not measured; local transition/contact surveys and product identity unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="145" customHeight="1">
+      <x:c r="A12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K07</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC contacts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>All 12 STCs contact bare pipe locally, including on insulated parent regions.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Do not turn local bare contact into whole-leg bare coverage. Footprints/windows/attachment response unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="145" customHeight="1">
+      <x:c r="A13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K08</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Main sensor map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>16 working numbered STC/PTC mappings populated in Sensors; STC5 B+942.186081 mm, PTC4 H+63.716137 mm.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Current working binding; physical tips, serials and historical change dates unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="145" customHeight="1">
+      <x:c r="A14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K09</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Jacket map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>JTC-B = PTC5 inlet; JTC-A = PTC6 outlet. Port reference positions in WORK; no main-loop station invented.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; Native channels</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Internal flow routing and actual wetted measurement planes unverified.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="145" customHeight="1">
+      <x:c r="A15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Sensor inventory and exclusions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>22 active geometric references: 12 STC + 4 main PTC + 4 LF + 2 JTC; 20 on main loop. Original 23 includes excluded PTC-X. Native core register has 20 channels incl. Amb/Tank.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>WORK; XWALK; Review issues I04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC-X excluded from active records, not asserted physically removed. LF mounts are not fiber active extents/channels.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="145" customHeight="1">
+      <x:c r="A16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Observation operators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC outside-wall surface; PTC1-4 centerline primary fluid is a working assumption. Amb/Tank lack accepted XYZ.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>XWALK; ASSUME ASM-023; VSEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD references remain pipe points/mounts, never certified sensing junctions. Angles/radii remain blank.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="145" customHeight="1">
+      <x:c r="A17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Calibration and DAQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Instrument certificates, corrections, Type B uncertainties, coverage factors and response are unknown. Sep2/4 native sampling about 30 Hz, scoped to those runs.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; FOLLOW; Calibration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Do not invent calibrations from noise statistics or assign one rate/clock/filter globally.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="145" customHeight="1">
+      <x:c r="A18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K13</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Heater source</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Electrical mat/band heaters reported; modeling extent full projected H-A. Real energized boundaries/power/efficiency/spatial split remain unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>HEAT; VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Measured Active heater span remains blank; voltage is not watts; clamp positions are mechanical only.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="145" customHeight="1">
+      <x:c r="A19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K14</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Cooler geometry and boundaries</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Shell 1017.5875 mm; complete jacket 1030.2875 mm; envelope starts D+127.56180941009107 mm. Bare pipe under jacket exchanges with coolant.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>WORK; CAD dimensions; CURRENT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Active cooling extent, coolant flow and contact/routing unresolved; envelope is not automatically active area.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="145" customHeight="1">
+      <x:c r="A20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Cooler cycling</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>User reports on/off chiller contributes to heated-plateau oscillation; conditional CAL-004 associations exist.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>OPCYCLE; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No universal period/causality; need controller/switching logs. Separate settled cycle mean from instantaneous equilibrium.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="145" customHeight="1">
+      <x:c r="A21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Fluids</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VCU options Prop-30 (reported 30% PG by mass), air, water; reported jacket water; primary fill/circuit must be matched to run.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>USER; PG; FLUIDCFG; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Product/formulation/batch/property functions and operating limits unverified; air has both ambient and possible primary roles.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="145" customHeight="1">
+      <x:c r="A22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K17</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Solid properties</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Nine candidate rho/cp/k functions already in Materials: pipe, fiberglass, heater ceramic. T in K; explicit SI outputs; out-of-range error.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VMAT; V5C</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working domains pipe 278.15-813 K, fiberglass 278.15-533 K, strip 278.15-1089 K. 5 C extension authorized; not validated, calibration-eligible or operating limits.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="145" customHeight="1">
+      <x:c r="A23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K18</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Topology and branches</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Each CAD exit tube 469.9 mm; top-exit/tank junction geometry does not certify hydraulics. Shared defaults omit BREP and retain TLEP with per-experiment temperature/pressure.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD dimensions; ASSUME ASM-020/021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Installed valves, vents, fill level and actual boundaries unknown. No-throughflow is not adiabatic.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="145" customHeight="1">
+      <x:c r="A24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K19</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Model and property selection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Physics model and effective reduced-zone model have separate observation/identification contracts; no fluid property model or facility closures approved here.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>MODEL; FLUIDCFG; Model choices</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No fitted constants imported or solver migration activated; property candidates calibration-ineligible.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="145" customHeight="1">
+      <x:c r="A25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Historical applicability</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC5 changed location; no change dates/run ranges. Earlier solver and diagnostic runs retain Rev8 and original insulation/material selections.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Never relabel historical results Rev9 or retroactively relocate sensors without run-specific evidence.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="145" customHeight="1">
+      <x:c r="A26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Experiment inventory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>23 native TDMS sources, 22 readable; 19 supplementary CSVs are not independent experiments. July29 waveform unreadable. Sep2/4 provisional ambient candidates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; TRIAGE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Shape labels are exploratory, not evidence of heater commands/fluid identity or accepted steady intervals.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="145" customHeight="1">
+      <x:c r="A27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Known data-quality failures</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>June12 STC6/PTC2/PTC3 include nonphysical Celsius readings. Retain raw, quarantine affected channel intervals and propagate versioned masks; retain unaffected channels.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DAQISS; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Cause/status/scaling unresolved. June17 auxiliary heater temperatures need separate screens; June17/23 transitions need event interpretation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="145" customHeight="1">
+      <x:c r="A28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Noise and uncertainty</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Slow correlated temperature motion persists with averaging; compact ten-second block results are not valid independent-block accuracy bars. CAL-004 explores temporal correlation/covariance.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No universal noise floor, absolute accuracy, optimal averaging or validated block length established; Type B absent.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="145" customHeight="1">
+      <x:c r="A29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Run identity and events</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Short July15 ambient-named acquisition may be same liquid experiment; clocks and media need confirmation. Chiller, heater and jolt events require run-specific logs.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>TRIAGE; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Do not call it an independent air-only test from filename or fit material constants without boundary/validity qualification.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="145" customHeight="1">
+      <x:c r="A30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Identification and validation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Relaxation gives time constants/parameter ratios without an absolute power or fixed-capacitance anchor. Existing fits/holdouts are conditional studies, not facility validation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>MODEL; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Approve intended-use tolerances, identifiability, calibration/withheld split and frozen model before accuracy claims.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="145" customHeight="1">
+      <x:c r="A31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>K26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Remaining experimental returns</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Need installed surveys and dated photos, sensor identities/depths, calibration/DAQ status, real heater power/wiring, coolant flow/route/control, fluid batch, boundary states and historical dates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Requirements; Review issues; Phase requests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Plans P0-P4 remain draft; records do not authorize operation or establish Nick approval.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="Rbd789b6a13c34804"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -1032,7 +2448,7 @@
       </x:c>
       <x:c r="B7" s="9" t="inlineStr">
         <x:is>
-          <x:t>VCU-REV9-DRAFT-006</x:t>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" s="8" t="str">
@@ -1054,8 +2470,10 @@
       <x:c r="A9" s="8" t="str">
         <x:v>Geometry source</x:v>
       </x:c>
-      <x:c r="B9" s="9" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08)</x:v>
+      <x:c r="B9" s="9" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08); WORK v3 working selection</x:t>
+        </x:is>
       </x:c>
       <x:c r="C9" s="8" t="str">
         <x:v>Companion source records are in reference/.</x:v>
@@ -1133,7 +2551,7 @@
       </x:c>
       <x:c r="B16" s="9" t="inlineStr">
         <x:is>
-          <x:t>Codex; VCU reference synchronization requested by Andres Fierro</x:t>
+          <x:t>Codex / agent-root-cfg002; requested by Andres Fierro</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="8" t="str">
@@ -1175,8 +2593,10 @@
       <x:c r="A20" s="8" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="B20" s="9" t="str">
-        <x:v>Main-loop geometry and sensor-position prototype</x:v>
+      <x:c r="B20" s="9" t="inlineStr">
+        <x:is>
+          <x:t>VCU current understanding: Rev9 geometry, working channels, regional insulation, materials, boundaries and historical evidence limits</x:t>
+        </x:is>
       </x:c>
       <x:c r="C20" s="8" t="str">
         <x:v>Ports, branches and full control schematics are not yet drawn.</x:v>
@@ -1210,7 +2630,7 @@
       </x:c>
       <x:c r="B23" s="9" t="inlineStr">
         <x:is>
-          <x:t>GEO-010: all ten insulation regions synchronized: six ordinary-pipe fiberglass regions about 50.8 mm; heater ceramic strip only about 6.35 mm; three top D-E partitions Bare. Coverage Reported; thicknesses approximate estimates. LF-01 remains covered.</x:t>
+          <x:t>CFG-002: reconcile working STC/PTC channels and observation operators; add jacket/ambient/tank native register and current-knowledge audit; refresh requirements, cooler cycling and data-quality limits. Preserve geometry, material equations, insulation and unknown measured inputs.</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" s="9" t="str">
@@ -1367,14 +2787,20 @@
       <x:c r="B8" s="17" t="str">
         <x:v>Exact DAQ channel / units</x:v>
       </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>Unknown; do not enter STC-02 as channel without checking</x:v>
-      </x:c>
-      <x:c r="D8" s="18" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="str">
-        <x:v>SNS channel_label_in_CAD blank</x:v>
+      <x:c r="C8" s="18" t="inlineStr">
+        <x:is>
+          <x:t>STC-02 -&gt; STC2, user-selected Rev9 working binding</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="18" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; historical run applicability/calibration unresolved</x:t>
+        </x:is>
       </x:c>
       <x:c r="F8" s="19"/>
       <x:c r="G8" s="19"/>
@@ -2469,28 +3895,52 @@
       <x:c r="H9" s="17" t="str">
         <x:v>Sheet 8 source identity</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="str">
-        <x:v>Rev9 STEP SHA-256 78c6ae52bf39084fbd9b1306d28dcbe2c1c4d5fccd334b0e68c861022a1bfbcf</x:v>
-      </x:c>
-      <x:c r="J9" s="17" t="str">
-        <x:v>CAD-derived</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="str">
-        <x:v>R9</x:v>
-      </x:c>
-      <x:c r="L9" s="17" t="str">
-        <x:v>Sheet 8</x:v>
-      </x:c>
-      <x:c r="M9" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N9" s="17" t="str">
-        <x:v>Does this source match installed VCU hardware?</x:v>
-      </x:c>
-      <x:c r="O9" s="19"/>
-      <x:c r="P9" s="19"/>
+      <x:c r="I9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Rev9 is user-selected best current geometry for new work; existing solver/results remain versioned Rev8.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Confirm installed configuration and dates; no physical release implied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O9" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Rev9 for new configuration documentation; no historical run migration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P9" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q9" s="19"/>
-      <x:c r="R9" s="19"/>
+      <x:c r="R9" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="10" ht="95" customHeight="1">
       <x:c r="A10" s="17" t="str">
@@ -2613,28 +4063,52 @@
       <x:c r="H12" s="17" t="str">
         <x:v>Method geometry map; sheets 1-2</x:v>
       </x:c>
-      <x:c r="I12" s="17" t="str">
-        <x:v>Inclined CAD cylinder axes 10.800 deg to horizontal</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="str">
-        <x:v>CAD-derived</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="str">
-        <x:v>R9</x:v>
-      </x:c>
-      <x:c r="L12" s="17" t="str">
-        <x:v>Sheets 1-2</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N12" s="17" t="str">
-        <x:v>What is the measured installed tilt and uncertainty?</x:v>
-      </x:c>
-      <x:c r="O12" s="19"/>
-      <x:c r="P12" s="19"/>
+      <x:c r="I12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Geometry-derived inclined axes about 10.8 deg; working local gravity (0,-1,0). Installed gravity survey absent.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Installed tilt/gravity and uncertainty still need survey.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O12" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use current local drawing frame and geometry-derived inclination provisionally</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P12" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q12" s="19"/>
-      <x:c r="R12" s="19"/>
+      <x:c r="R12" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="13" ht="95" customHeight="1">
       <x:c r="A13" s="17" t="str">
@@ -3183,28 +4657,52 @@
       <x:c r="H23" s="17" t="str">
         <x:v>Fluid scope; facility/fluid configuration</x:v>
       </x:c>
-      <x:c r="I23" s="17" t="str">
-        <x:v>VCU options: Prop-30, air, water; no circuit assignment established</x:v>
-      </x:c>
-      <x:c r="J23" s="17" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="str">
-        <x:v>USER</x:v>
-      </x:c>
-      <x:c r="L23" s="17" t="str">
-        <x:v>Fluid clarification in chat</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N23" s="17" t="str">
-        <x:v>Which fluid occupies each circuit in this run?</x:v>
-      </x:c>
-      <x:c r="O23" s="19"/>
-      <x:c r="P23" s="19"/>
+      <x:c r="I23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VCU options Prop-30/air/water; primary fill selected per run. Jacket water reported; ambient air role distinct.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>USER; FLUIDCFG; XWALK; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N23" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Confirm fluid/batch in each acquisition; ambient filename alone is insufficient.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O23" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Run-specific primary fill; reported water jacket coolant</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P23" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q23" s="19"/>
-      <x:c r="R23" s="19"/>
+      <x:c r="R23" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="24" ht="95" customHeight="1">
       <x:c r="A24" s="17" t="str">
@@ -3327,28 +4825,52 @@
       <x:c r="H26" s="17" t="str">
         <x:v>Instrumentation documentation; sensor rows</x:v>
       </x:c>
-      <x:c r="I26" s="17" t="str">
-        <x:v>12 STC, 4 LF, 5 loop PTC and 2 JTC geometric references</x:v>
-      </x:c>
-      <x:c r="J26" s="17" t="str">
-        <x:v>CAD-derived</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="str">
-        <x:v>R9</x:v>
-      </x:c>
-      <x:c r="L26" s="17" t="str">
-        <x:v>Sheet 5 inventory</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N26" s="17" t="str">
-        <x:v>Verify installed hardware count and channel identities for remaining sensors. PTC-X was removed from the active register at the repository owner's request on 2026-10-16; no physical removal is asserted.</x:v>
-      </x:c>
-      <x:c r="O26" s="19"/>
-      <x:c r="P26" s="19"/>
+      <x:c r="I26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Active geometry: 12 STC, 4 main PTC, 4 LF and 2 JTC = 22 references; 20 main-loop references. Original extraction has 23 including excluded PTC-X. Native core inventory has 20 channels incl. Amb/Tank; LF is not mapped.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N26" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Installed inventory, serials and fiber channels still need evidence.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O26" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Exclude PTC-X from active register; preserve original reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P26" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q26" s="19"/>
-      <x:c r="R26" s="19"/>
+      <x:c r="R26" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="27" ht="95" customHeight="1">
       <x:c r="A27" s="17" t="str">
@@ -3423,28 +4945,52 @@
       <x:c r="H28" s="17" t="str">
         <x:v>Method instrumentation documentation</x:v>
       </x:c>
-      <x:c r="I28" s="17" t="str">
-        <x:v>Unverified; STEP does not encode acquisition-channel labels</x:v>
-      </x:c>
-      <x:c r="J28" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="str">
-        <x:v>SNS</x:v>
-      </x:c>
-      <x:c r="L28" s="17" t="str">
-        <x:v>channel_label_in_CAD blank; label_basis</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N28" s="17" t="str">
-        <x:v>Trace cable/DAQ configuration and verify the mapping with a recorded check.</x:v>
-      </x:c>
-      <x:c r="O28" s="19"/>
-      <x:c r="P28" s="19"/>
+      <x:c r="I28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>User-selected STC1-12/PTC1-4 matching Rev9 references; JTC-B=PTC5 inlet and JTC-A=PTC6 outlet. Amb/Tank native names have no accepted XYZ.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N28" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Verify cable/DAQ identity and historical run applicability; do not map by name alone.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O28" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use Native channels working register; LF remains unbound</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P28" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q28" s="19"/>
-      <x:c r="R28" s="19"/>
+      <x:c r="R28" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="29" ht="95" customHeight="1">
       <x:c r="A29" s="17" t="str">
@@ -3471,28 +5017,52 @@
       <x:c r="H29" s="17" t="str">
         <x:v>nearest_endpoint, nearest_distance_mm</x:v>
       </x:c>
-      <x:c r="I29" s="17" t="str">
-        <x:v>STC-02: upcomer, B + 116.686 mm geometric reference</x:v>
-      </x:c>
-      <x:c r="J29" s="17" t="str">
-        <x:v>CAD-derived</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="str">
-        <x:v>SNS</x:v>
-      </x:c>
-      <x:c r="L29" s="17" t="str">
-        <x:v>sensor_id=STC-02</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N29" s="17" t="str">
-        <x:v>Measure the actual sensing/contact reference and identify the point basis.</x:v>
-      </x:c>
-      <x:c r="O29" s="19"/>
-      <x:c r="P29" s="19"/>
+      <x:c r="I29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Rev9 axial references preserved; STC5 is B+942.186081 mm, PTC4 H+63.716137 mm. User selects these for new work.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAD-derived</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Survey actual sensing/contact point and historical installation dates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O29" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use Rev9 axial references; physical sensing tips remain unknown</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P29" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q29" s="19"/>
-      <x:c r="R29" s="19"/>
+      <x:c r="R29" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="30" ht="95" customHeight="1">
       <x:c r="A30" s="17" t="str">
@@ -3615,28 +5185,52 @@
       <x:c r="H32" s="17" t="str">
         <x:v>Method instrumentation documentation</x:v>
       </x:c>
-      <x:c r="I32" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J32" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L32" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M32" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N32" s="17" t="str">
-        <x:v>Describe attachment, contact, insulation position and time response.</x:v>
-      </x:c>
-      <x:c r="O32" s="19"/>
-      <x:c r="P32" s="19"/>
+      <x:c r="I32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>All STCs contact bare pipe locally per user; insulated parent regions remain per CURRENT. LF-01 locally covered. Actual attachment details unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; VTOP; CURRENT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Attachment, window width, junction footprint, response and local contact resistance unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O32" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Bare local STC contact; do not infer whole parent leg bare</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P32" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q32" s="19"/>
-      <x:c r="R32" s="19"/>
+      <x:c r="R32" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="33" ht="95" customHeight="1">
       <x:c r="A33" s="17" t="str">
@@ -3807,28 +5401,52 @@
       <x:c r="H36" s="17" t="str">
         <x:v>Instrumentation documentation and logging</x:v>
       </x:c>
-      <x:c r="I36" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J36" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L36" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M36" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N36" s="17" t="str">
-        <x:v>Supply evidence and request review.</x:v>
-      </x:c>
-      <x:c r="O36" s="19"/>
-      <x:c r="P36" s="19"/>
+      <x:c r="I36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Approximately 30 Hz native sampling documented for Sep2/4 only. Filtering/scaling and lag remain run-specific and unqualified.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Need instrument response, scaling/filtering and status-code evidence.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O36" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use native timebase and per-run metadata; no universal sample-rate assignment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P36" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q36" s="19"/>
-      <x:c r="R36" s="19"/>
+      <x:c r="R36" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="37" ht="95" customHeight="1">
       <x:c r="A37" s="17" t="str">
@@ -3903,28 +5521,52 @@
       <x:c r="H38" s="17" t="str">
         <x:v>P0 acceptance-channel matrix; P1 TC-Luna comparison</x:v>
       </x:c>
-      <x:c r="I38" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J38" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L38" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M38" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N38" s="17" t="str">
-        <x:v>Which channels are mandatory, and which alternates are approved with evidence?</x:v>
-      </x:c>
-      <x:c r="O38" s="19"/>
-      <x:c r="P38" s="19"/>
+      <x:c r="I38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Main-loop observations STC1-12/PTC1-4; jacket PTC5/6; Amb/Tank auxiliary; LF geometric only. No blanket mandatory-channel acceptance rule selected.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Preapprove mandatory/alternate roles for each intended use.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O38" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Working roles in Native channels</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P38" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q38" s="19"/>
-      <x:c r="R38" s="19"/>
+      <x:c r="R38" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="39" ht="95" customHeight="1">
       <x:c r="A39" s="17" t="str">
@@ -4199,28 +5841,52 @@
       <x:c r="H44" s="17" t="str">
         <x:v>Method secondary-side energy-balance boundaries</x:v>
       </x:c>
-      <x:c r="I44" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J44" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L44" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M44" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N44" s="17" t="str">
-        <x:v>Confirm actual inlet/outlet, intervening hoses, bypasses, heat leaks and sensor planes.</x:v>
-      </x:c>
-      <x:c r="O44" s="19"/>
-      <x:c r="P44" s="19"/>
+      <x:c r="I44" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working jacket inlet JTC-B/PTC5, outlet JTC-A/PTC6; detailed internal routing and wetted sensing planes unverified.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J44" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K44" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L44" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M44" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N44" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Confirm run-specific hoses, bypasses and physical sensing planes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O44" s="19" t="inlineStr">
+        <x:is>
+          <x:t>JTC-B/PTC5 inlet; JTC-A/PTC6 outlet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P44" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q44" s="19"/>
-      <x:c r="R44" s="19"/>
+      <x:c r="R44" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="45" ht="95" customHeight="1">
       <x:c r="A45" s="17" t="str">
@@ -4247,28 +5913,52 @@
       <x:c r="H45" s="17" t="str">
         <x:v>Secondary-side boundaries</x:v>
       </x:c>
-      <x:c r="I45" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J45" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L45" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M45" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N45" s="17" t="str">
-        <x:v>Supply flow-meter basis, calibration, fluid properties, temperatures and signs.</x:v>
-      </x:c>
-      <x:c r="O45" s="19"/>
-      <x:c r="P45" s="19"/>
+      <x:c r="I45" s="17" t="inlineStr">
+        <x:is>
+          <x:t>PTC5/6 provide working inlet/outlet temperatures; coolant flow calibration and physical planes are unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J45" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K45" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L45" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M45" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N45" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Obtain measured coolant flow, units, calibration, properties and timing.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O45" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use temperature roles provisionally; do not invent flow or measured duty</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P45" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q45" s="19"/>
-      <x:c r="R45" s="19"/>
+      <x:c r="R45" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="46" ht="95" customHeight="1">
       <x:c r="A46" s="17" t="str">
@@ -4295,28 +5985,52 @@
       <x:c r="H46" s="17" t="str">
         <x:v>Method logging and time synchronization</x:v>
       </x:c>
-      <x:c r="I46" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J46" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K46" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L46" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M46" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N46" s="17" t="str">
-        <x:v>Supply evidence and request review.</x:v>
-      </x:c>
-      <x:c r="O46" s="19"/>
-      <x:c r="P46" s="19"/>
+      <x:c r="I46" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Chiller on/off contributes to hot-plateau oscillations per user. CAL-004 finds provisional temperature associations, not control causality.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J46" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K46" s="17" t="inlineStr">
+        <x:is>
+          <x:t>OPCYCLE; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L46" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M46" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N46" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Need controller sensor, setpoint/deadband, switching and exact intervals.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O46" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Treat oscillatory plateaus as potentially cyclic operation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P46" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q46" s="19"/>
-      <x:c r="R46" s="19"/>
+      <x:c r="R46" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="47" ht="95" customHeight="1">
       <x:c r="A47" s="17" t="str">
@@ -4439,28 +6153,52 @@
       <x:c r="H49" s="17" t="str">
         <x:v>Method environmental and condensation measurements</x:v>
       </x:c>
-      <x:c r="I49" s="17" t="str">
-        <x:v>Draft calls for two room T/RH stations and cold exposed-surface measurements</x:v>
-      </x:c>
-      <x:c r="J49" s="17" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="K49" s="17" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="L49" s="17" t="str">
-        <x:v>Method environmental measurements</x:v>
-      </x:c>
-      <x:c r="M49" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N49" s="17" t="str">
-        <x:v>Are these channels installed? Under-insulation wall TCs are not exposed-surface measurements.</x:v>
-      </x:c>
-      <x:c r="O49" s="19"/>
-      <x:c r="P49" s="19"/>
+      <x:c r="I49" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Amb is a native ambient reference with unaccepted coordinates; room RH/two-station installation unverified. Bare STC contact does not establish an exposed ambient-surface measurement.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J49" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K49" s="17" t="inlineStr">
+        <x:is>
+          <x:t>XWALK; VSEL; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L49" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M49" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N49" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Identify room sensor placement and actual exposed surface channels.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O49" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Retain Amb role without inventing XYZ or RH channels</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P49" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q49" s="19"/>
-      <x:c r="R49" s="19"/>
+      <x:c r="R49" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="50" ht="95" customHeight="1">
       <x:c r="A50" s="17" t="str">
@@ -4535,28 +6273,52 @@
       <x:c r="H51" s="17" t="str">
         <x:v>Campaign execution conventions; Phase 4 records</x:v>
       </x:c>
-      <x:c r="I51" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J51" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K51" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L51" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M51" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N51" s="17" t="str">
-        <x:v>Supply evidence and request review.</x:v>
-      </x:c>
-      <x:c r="O51" s="19"/>
-      <x:c r="P51" s="19"/>
+      <x:c r="I51" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VCU inventory: 23 native sources, 22 readable; 19 CSVs are supplementary, not independent experiments. July29 unreadable; preserve hashes and run/event records.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J51" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K51" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; TRIAGE; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L51" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M51" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N51" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No universal experiment/fluid assignment; July15 ambient-named file may be liquid continuation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O51" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use source/run hashes and run-specific event logs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P51" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q51" s="19"/>
-      <x:c r="R51" s="19"/>
+      <x:c r="R51" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="52" ht="95" customHeight="1">
       <x:c r="A52" s="17" t="str">
@@ -4631,28 +6393,52 @@
       <x:c r="H53" s="17" t="str">
         <x:v>Run outputs; model freeze</x:v>
       </x:c>
-      <x:c r="I53" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J53" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K53" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L53" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M53" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N53" s="17" t="str">
-        <x:v>Record solver/code revision, resolved configuration and property version.</x:v>
-      </x:c>
-      <x:c r="O53" s="19"/>
-      <x:c r="P53" s="19"/>
+      <x:c r="I53" s="17" t="inlineStr">
+        <x:is>
+          <x:t>This documentation uses WORK v3 / regional v7 / material v3. Historical numerical studies keep original Rev8/insulation-v5 inputs.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J53" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K53" s="17" t="inlineStr">
+        <x:is>
+          <x:t>WORK; CURRENT; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L53" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M53" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N53" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Record actual solver/input/property versions separately in every run.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O53" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007 for current documentation only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P53" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q53" s="19"/>
-      <x:c r="R53" s="19"/>
+      <x:c r="R53" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="54" ht="95" customHeight="1">
       <x:c r="A54" s="17" t="str">
@@ -4735,28 +6521,52 @@
       <x:c r="H55" s="17" t="str">
         <x:v>Method geometry/model map</x:v>
       </x:c>
-      <x:c r="I55" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J55" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K55" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L55" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M55" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N55" s="17" t="str">
-        <x:v>Map physical sensing points or averages to cells/regions; include non-coincident offsets.</x:v>
-      </x:c>
-      <x:c r="O55" s="19"/>
-      <x:c r="P55" s="19"/>
+      <x:c r="I55" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STCs observe outside wall locally on bare pipe; PTC1-4 treated as centerline fluid; JTC/PTC5/6 are jacket boundaries, not main-loop nodes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J55" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K55" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L55" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M55" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N55" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Actual junction depths, response, finite footprints and mesh interpolation unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O55" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Working observation operators in Calibration and Native channels</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P55" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q55" s="19"/>
-      <x:c r="R55" s="19"/>
+      <x:c r="R55" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="56" ht="95" customHeight="1">
       <x:c r="A56" s="17" t="str">
@@ -4831,28 +6641,52 @@
       <x:c r="H57" s="17" t="str">
         <x:v>Model stages; reduced-zone thermal model</x:v>
       </x:c>
-      <x:c r="I57" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J57" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K57" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L57" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M57" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N57" s="17" t="str">
-        <x:v>Which layers, axial paths, capacitances and contacts are included?</x:v>
-      </x:c>
-      <x:c r="O57" s="19"/>
-      <x:c r="P57" s="19"/>
+      <x:c r="I57" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Perfect insulation contact is a user-directed modeling assumption; local bare STCs and distinct fiberglass/ceramic regions retained.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J57" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K57" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VINS; VSEL; CURRENT; ASSUME</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L57" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M57" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N57" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Model-specific storage, axial paths and contact sensitivity require review.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O57" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Keep separate fluid/wall/insulation paths and declared contact assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P57" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q57" s="19"/>
-      <x:c r="R57" s="19"/>
+      <x:c r="R57" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="58" ht="95" customHeight="1">
       <x:c r="A58" s="17" t="str">
@@ -4879,28 +6713,52 @@
       <x:c r="H58" s="17" t="str">
         <x:v>Exit-pipe alignment request; configuration record</x:v>
       </x:c>
-      <x:c r="I58" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J58" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K58" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L58" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M58" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N58" s="17" t="str">
-        <x:v>Specify termination plane, mass/pressure and thermal conditions; no throughflow does not imply adiabatic.</x:v>
-      </x:c>
-      <x:c r="O58" s="19"/>
-      <x:c r="P58" s="19"/>
+      <x:c r="I58" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Shared default omits BREP (ASM-020) and retains TLEP with experiment-specific temperature/pressure (ASM-021). No installed VCU boundary values are known.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J58" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K58" s="17" t="inlineStr">
+        <x:is>
+          <x:t>ASSUME</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L58" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M58" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N58" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Select exact VCU termination planes and measured states before use; no-throughflow is not adiabatic.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O58" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Provisional model-domain defaults only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P58" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q58" s="19"/>
-      <x:c r="R58" s="19"/>
+      <x:c r="R58" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="59" ht="95" customHeight="1">
       <x:c r="A59" s="17" t="str">
@@ -4985,28 +6843,52 @@
       <x:c r="H60" s="17" t="str">
         <x:v>Secondary boundaries; cooler forms</x:v>
       </x:c>
-      <x:c r="I60" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J60" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K60" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L60" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M60" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N60" s="17" t="str">
-        <x:v>Choose measured inlet/flow, imposed wall temperature or coefficient model with rationale.</x:v>
-      </x:c>
-      <x:c r="O60" s="19"/>
-      <x:c r="P60" s="19"/>
+      <x:c r="I60" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working PTC5 inlet/PTC6 outlet; measured cooler forcing varies; user reports chiller cycling. Coefficient/flow and active-span choices unresolved.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J60" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K60" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; OPCYCLE; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L60" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M60" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N60" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Need flow, routing, controller logs and qualified boundary/model choice.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O60" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Run-specific cooler input; compare cyclic mean/amplitude separately</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P60" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q60" s="19"/>
-      <x:c r="R60" s="19"/>
+      <x:c r="R60" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="61" ht="95" customHeight="1">
       <x:c r="A61" s="17" t="str">
@@ -5033,28 +6915,52 @@
       <x:c r="H61" s="17" t="str">
         <x:v>Reduced-zone heat loss; thermal network</x:v>
       </x:c>
-      <x:c r="I61" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J61" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K61" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L61" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M61" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N61" s="17" t="str">
-        <x:v>Record ambient assignment, emissivity, surface state, correlations and validity.</x:v>
-      </x:c>
-      <x:c r="O61" s="19"/>
-      <x:c r="P61" s="19"/>
+      <x:c r="I61" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported insulated regions and bare D-E are known; jacket heat exchange is with water where present. Ambient coupling/emissivity unresolved.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J61" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K61" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CURRENT; VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L61" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M61" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N61" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Select qualified correlations, surface states, supports and ambient assignment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O61" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Separate room-air loss from coolant exchange</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P61" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q61" s="19"/>
-      <x:c r="R61" s="19"/>
+      <x:c r="R61" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="62" ht="95" customHeight="1">
       <x:c r="A62" s="17" t="str">
@@ -5611,28 +7517,52 @@
       <x:c r="H72" s="17" t="str">
         <x:v>Model map; effective initial states</x:v>
       </x:c>
-      <x:c r="I72" s="17" t="str">
-        <x:v>Reduced-zone temperature is an effective state, not automatically fluid/wall temperature</x:v>
-      </x:c>
-      <x:c r="J72" s="17" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="K72" s="17" t="str">
-        <x:v>P2; MODEL</x:v>
-      </x:c>
-      <x:c r="L72" s="17" t="str">
-        <x:v>Reduced-zone model; reduced-zone paragraph</x:v>
-      </x:c>
-      <x:c r="M72" s="17" t="str">
-        <x:v>Needs review</x:v>
-      </x:c>
-      <x:c r="N72" s="17" t="str">
-        <x:v>Define spatial/time averaging, lag and fluid-wall weighting.</x:v>
-      </x:c>
-      <x:c r="O72" s="19"/>
-      <x:c r="P72" s="19"/>
+      <x:c r="I72" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC wall and assumed PTC centerline operators are explicit. Distributed optical extent and sensor lag unknown; reduced-zone states need their own averaging rule.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J72" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K72" s="17" t="inlineStr">
+        <x:is>
+          <x:t>XWALK; VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L72" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M72" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N72" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Qualify lag/spatial/time averaging and noncoincident comparisons.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O72" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Do not equate effective-zone temperature with fluid or wall automatically</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P72" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q72" s="19"/>
-      <x:c r="R72" s="19"/>
+      <x:c r="R72" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="73" ht="95" customHeight="1">
       <x:c r="A73" s="17" t="str">
@@ -5659,28 +7589,52 @@
       <x:c r="H73" s="17" t="str">
         <x:v>Section 2 Data Acceptance and Uncertainty</x:v>
       </x:c>
-      <x:c r="I73" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J73" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K73" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L73" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M73" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N73" s="17" t="str">
-        <x:v>Approve intended-use limits and demonstrate resolvability; do not loosen them to fit noise.</x:v>
-      </x:c>
-      <x:c r="O73" s="19"/>
-      <x:c r="P73" s="19"/>
+      <x:c r="I73" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Sep2/4 are provisional ambient baseline candidates; stable mean cyclic operation differs from instantaneous equilibrium. No accepted comparison tolerances established.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J73" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K73" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; FOLLOW; OPCYCLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L73" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M73" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N73" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Approve intended-use tolerances and qualify run-specific intervals.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O73" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Keep exploratory classifications separate from accepted steady-state limits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P73" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q73" s="19"/>
-      <x:c r="R73" s="19"/>
+      <x:c r="R73" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="74" ht="95" customHeight="1">
       <x:c r="A74" s="17" t="str">
@@ -5755,28 +7709,52 @@
       <x:c r="H75" s="17" t="str">
         <x:v>Required Outputs: correlation structure and uncertainty</x:v>
       </x:c>
-      <x:c r="I75" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J75" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K75" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L75" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M75" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N75" s="17" t="str">
-        <x:v>Freeze block/window rules, Type A/B and shared-error covariance with evidence.</x:v>
-      </x:c>
-      <x:c r="O75" s="19"/>
-      <x:c r="P75" s="19"/>
+      <x:c r="I75" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Slow correlated variation persists after averaging; ten-second block means are not independent. CAL-004 temporal-block analyses address serial dependence; Type B calibration unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J75" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K75" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L75" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M75" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N75" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No universal validated block length, intrinsic noise floor or absolute accuracy supplied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O75" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Use temporal correlation and joint-channel covariance; report block sensitivity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P75" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q75" s="19"/>
-      <x:c r="R75" s="19"/>
+      <x:c r="R75" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="76" ht="95" customHeight="1">
       <x:c r="A76" s="17" t="str">
@@ -5803,28 +7781,52 @@
       <x:c r="H76" s="17" t="str">
         <x:v>P2 runs/freeze; P3 blind validation; P4 applicability case</x:v>
       </x:c>
-      <x:c r="I76" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J76" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K76" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L76" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M76" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N76" s="17" t="str">
-        <x:v>Declare run roles before fitting; record model/property/mapping versions and any reassignment.</x:v>
-      </x:c>
-      <x:c r="O76" s="19"/>
-      <x:c r="P76" s="19"/>
+      <x:c r="I76" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Existing acquisitions have working calibration roles, not independent validation; no blind Rev9 split established. Historical model/configurations remain frozen to their own inputs.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J76" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K76" s="17" t="inlineStr">
+        <x:is>
+          <x:t>FOLLOW; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L76" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M76" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N76" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Finalize scientific calibration/validation roles; empirical interval holdout is not facility validation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O76" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Declare held-out intervals/runs and model freeze before scoring</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P76" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q76" s="19"/>
-      <x:c r="R76" s="19"/>
+      <x:c r="R76" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="77" ht="95" customHeight="1">
       <x:c r="A77" s="17" t="str">
@@ -5851,28 +7853,52 @@
       <x:c r="H77" s="17" t="str">
         <x:v>Required Outputs steps 5-7</x:v>
       </x:c>
-      <x:c r="I77" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J77" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K77" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L77" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M77" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N77" s="17" t="str">
-        <x:v>Report parameter covariance, residual structure, start-time and initial-state sensitivity.</x:v>
-      </x:c>
-      <x:c r="O77" s="19"/>
-      <x:c r="P77" s="19"/>
+      <x:c r="I77" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Passive relaxation constrains time constants and parameter ratios; absolute conductance/capacitance scales need a fixed or measured-power anchor.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J77" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K77" s="17" t="inlineStr">
+        <x:is>
+          <x:t>MODEL; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L77" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M77" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N77" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No validated all-layer parameter identification or fitted properties imported.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O77" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Require identifiability and boundary/initial-state sensitivity before interpreting fitted material constants</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P77" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q77" s="19"/>
-      <x:c r="R77" s="19"/>
+      <x:c r="R77" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="78" ht="95" customHeight="1">
       <x:c r="A78" s="17" t="str">
@@ -5899,28 +7925,52 @@
       <x:c r="H78" s="17" t="str">
         <x:v>Slowest loop time constant; Required Outputs</x:v>
       </x:c>
-      <x:c r="I78" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J78" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K78" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L78" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M78" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N78" s="17" t="str">
-        <x:v>Report uncertainty and conservative supported bound; do not use an archived plateau fit.</x:v>
-      </x:c>
-      <x:c r="O78" s="19"/>
-      <x:c r="P78" s="19"/>
+      <x:c r="I78" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Response/settling estimates are conditional on boundary, interval and model. Oscillating hot plateaus need cycle metrics rather than assumed instantaneous settling.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J78" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K78" s="17" t="inlineStr">
+        <x:is>
+          <x:t>FOLLOW; OPCYCLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L78" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M78" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N78" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Qualify confidence, start-time, boundary variability and supported domain.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O78" s="19" t="inlineStr">
+        <x:is>
+          <x:t>No universal settling time selected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P78" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q78" s="19"/>
-      <x:c r="R78" s="19"/>
+      <x:c r="R78" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="79" ht="95" customHeight="1">
       <x:c r="A79" s="17" t="str">
@@ -6091,28 +8141,52 @@
       <x:c r="H82" s="17" t="str">
         <x:v>Validation and disposition sections</x:v>
       </x:c>
-      <x:c r="I82" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="J82" s="17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="K82" s="17" t="str">
-        <x:v>None supplied</x:v>
-      </x:c>
-      <x:c r="L82" s="17" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="M82" s="17" t="str">
-        <x:v>Needs information</x:v>
-      </x:c>
-      <x:c r="N82" s="17" t="str">
-        <x:v>Define metrics and acceptance basis; preserve blind comparisons and model limitations.</x:v>
-      </x:c>
-      <x:c r="O82" s="19"/>
-      <x:c r="P82" s="19"/>
+      <x:c r="I82" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Historical forward/boundary studies remain conditional; neither successful computation nor an empirical holdout validates the Rev9 facility model.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J82" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K82" s="17" t="inlineStr">
+        <x:is>
+          <x:t>FOLLOW; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L82" s="17" t="inlineStr">
+        <x:is>
+          <x:t>See cited Sources locators and Current knowledge / Native channels; CFG-002 evidence bundle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M82" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Needs review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N82" s="17" t="inlineStr">
+        <x:is>
+          <x:t>No validated facility accuracy or release criterion supplied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O82" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Retain conservation/uncertainty checks and predeclared unseen assessment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P82" s="19" t="inlineStr">
+        <x:is>
+          <x:t>Transferred documented working understanding; provisional use only; no installed or package release approval.</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q82" s="19"/>
-      <x:c r="R82" s="19"/>
+      <x:c r="R82" s="19" t="inlineStr">
+        <x:is>
+          <x:t>VCU-REV9-DRAFT-007</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="83" ht="95" customHeight="1">
       <x:c r="A83" s="17" t="str">
@@ -6828,7 +8902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
@@ -7110,10 +9184,121 @@
         <x:v>M12-M19</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>I10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Historical applicability</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; FOLLOW; DAQISS; OPCYCLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>STC5 changed location; Rev9 working map and historical Rev8 records have no installation date crosswalk.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Experimental + computational</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Provide dated sensor/geometry applicability per run; retain original model versions.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>C04; C23-C24; C46; M02</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>I11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Data validity and calibration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; FOLLOW; DAQISS; OPCYCLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>June12 nonphysical readings; Type B accuracy and status/scaling unqualified; slow temporal covariance matters.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Experimental + computational</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Resolve DAQ status; version masks and correlation-aware uncertainty; retain raw.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="17" t="inlineStr">
+        <x:is>
+          <x:t>C28-C32; M22-M24</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>I12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Boundary-control qualification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; FOLLOW; DAQISS; OPCYCLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Chiller contribution reported; internal jacket route, flow, controller identity and switching logs absent.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Experimental + computational</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Confirm PTC5/6 run-specific planes and controller/flow logs before causal or duty claims.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="17" t="inlineStr">
+        <x:is>
+          <x:t>C39-C41; M09; M27</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9e02aec8f064b4d"/>
+    <x:tablePart r:id="Rf9e02aec8f064b4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7571,7 +9756,7 @@
       </x:c>
       <x:c r="E26" s="17" t="inlineStr">
         <x:is>
-          <x:t>Regional thickness estimates/contact assumption; exact transitions and installed construction unverified. VSEL is later controlling top-leg evidence.</x:t>
+          <x:t>Historical regional v5. Current coverage is VREG/CURRENT and WORK v3; all STC contacts bare per VSEL. Preserve v5 as provenance only.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7626,6 +9811,276 @@
       <x:c r="E28" s="17" t="inlineStr">
         <x:is>
           <x:t>Reported coverage and approximate thickness estimates; product/fit validation, installed surveys and historical applicability remain separate.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/WORK_rev9_working_selection_v3.json</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Rev9 working selection v3; GEO-010 2026-10-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>sensors, heater, jacket, insulation; historical_run_applicability</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working choices; not installed survey, calibration or historical run migration.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/XWALK_2026-10-05_VCU_WORKING_SENSOR_CROSSWALK.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>2026-10-05 historical Rev8 crosswalk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Working measurement operators and native channel roles</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Use radial operators/native roles only; Rev8 stations, old insulation and unpaired JTC wording superseded by VSEL/VREG/WORK.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DIAG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/DIAG_README.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAL-003 2026-10-08</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Quality issues; ambient correlation; chiller operator report</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Installed-system diagnostics, not sensor accuracy; compact ten-second blocks remain correlated. CAL-004 follow-up supersedes initial masks/method limitations.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/FOLLOW_README.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAL-004 2026-10-08 follow-up</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Native validity; temporal uncertainty; heated associations; forward comparisons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Conditional historical Rev8/insulation-v5 analysis. Numerical correlations do not prove controller causality or validate Rev9.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="17" t="inlineStr">
+        <x:is>
+          <x:t>DAQISS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/DAQISS_EXPERIMENTAL_TEAM_CLARIFICATION.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="17" t="inlineStr">
+        <x:is>
+          <x:t>2026-10-08 source-linked clarification draft</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="17" t="inlineStr">
+        <x:is>
+          <x:t>June12 source hash and channel invalid counts; June17/23 events</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Draft for user to send; not sent and not answered.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="17" t="inlineStr">
+        <x:is>
+          <x:t>OPCYCLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/OPCYCLE_operator_update.json</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Direct user report 2026-10-08</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="17" t="inlineStr">
+        <x:is>
+          <x:t>statements and unknown</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Chiller on/off contributes to hot-plateau oscillation; exact intervals/control logs unknown.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="17" t="inlineStr">
+        <x:is>
+          <x:t>TRIAGE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/TRIAGE_README.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CAL-003 2026-10-07</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="17" t="inlineStr">
+        <x:is>
+          <x:t>July15 identity/clock limits; July29 source</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Short ambient-named July15 file may be same liquid experiment; not independently established air run.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>FLUIDCFG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/FLUIDCFG_fluid.yaml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Provisional identity configuration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>identity, unresolved, runtime_property_selection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Prop-30 identity candidate; no selected numerical fluid property model. Later USER reports 30% mass basis.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="17" t="inlineStr">
+        <x:is>
+          <x:t>ASSUME</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/ASSUME_ASSUMPTIONS.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Snapshot read 2026-10-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" s="17" t="inlineStr">
+        <x:is>
+          <x:t>ASM-020/021/022/023/026/027; later VSEL/VREG overrides</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Shared model defaults are modeling choices, not observed VCU valve states. Historical heater lengths/contact/ranges superseded by later dated decisions.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>CURRENT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>support/evidence/2026-10-16_CFG-002_vcu_current_understanding/CURRENT_INSULATION_CURRENT.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>GEO-010 2026-10-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Regional assignment table and qualifications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Current reported coverage; estimated thickness; not product confirmation.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8774,18 +11229,28 @@
       </x:c>
       <x:c r="F6" s="10"/>
       <x:c r="G6" s="10"/>
-      <x:c r="H6" s="8"/>
-      <x:c r="I6" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J6" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K6" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L6" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC2 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
@@ -8806,18 +11271,28 @@
       </x:c>
       <x:c r="F7" s="10"/>
       <x:c r="G7" s="10"/>
-      <x:c r="H7" s="8"/>
-      <x:c r="I7" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J7" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K7" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L7" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC3 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
@@ -8838,18 +11313,28 @@
       </x:c>
       <x:c r="F8" s="10"/>
       <x:c r="G8" s="10"/>
-      <x:c r="H8" s="8"/>
-      <x:c r="I8" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J8" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K8" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L8" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC4 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
@@ -8870,18 +11355,28 @@
       </x:c>
       <x:c r="F9" s="10"/>
       <x:c r="G9" s="10"/>
-      <x:c r="H9" s="8"/>
-      <x:c r="I9" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J9" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K9" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L9" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC5 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Changed location: use Rev9 B+942.186081 mm for new work; change date not supplied. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
@@ -8936,18 +11431,28 @@
       </x:c>
       <x:c r="F11" s="10"/>
       <x:c r="G11" s="10"/>
-      <x:c r="H11" s="8"/>
-      <x:c r="I11" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J11" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K11" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L11" s="8" t="str">
-        <x:v>CAD body-to-pipe gap 0.0000 mm; contact unverified.</x:v>
+      <x:c r="K11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC6 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. CAD body-to-pipe gap 0.0000 mm; contact unverified. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
@@ -8968,18 +11473,28 @@
       </x:c>
       <x:c r="F12" s="10"/>
       <x:c r="G12" s="10"/>
-      <x:c r="H12" s="8"/>
-      <x:c r="I12" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J12" s="8" t="str">
         <x:v>Mount reference</x:v>
       </x:c>
-      <x:c r="K12" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L12" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel PTC1 (2026-10-14); axial reference remains CAD-derived. XWALK/ASM-023: centerline fluid temperature is a working observation assumption, not a measured junction depth. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
@@ -9000,18 +11515,28 @@
       </x:c>
       <x:c r="F13" s="10"/>
       <x:c r="G13" s="10"/>
-      <x:c r="H13" s="8"/>
-      <x:c r="I13" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J13" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K13" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L13" s="8" t="str">
-        <x:v>CAD body-to-pipe gap 0.0000 mm; contact unverified.</x:v>
+      <x:c r="K13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC7 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. CAD body-to-pipe gap 0.0000 mm; contact unverified. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
@@ -9064,18 +11589,28 @@
       </x:c>
       <x:c r="F15" s="10"/>
       <x:c r="G15" s="10"/>
-      <x:c r="H15" s="8"/>
-      <x:c r="I15" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J15" s="8" t="str">
         <x:v>Mount reference</x:v>
       </x:c>
-      <x:c r="K15" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L15" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel PTC3 (2026-10-14); axial reference remains CAD-derived. XWALK/ASM-023: centerline fluid temperature is a working observation assumption, not a measured junction depth. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
@@ -9096,18 +11631,28 @@
       </x:c>
       <x:c r="F16" s="10"/>
       <x:c r="G16" s="10"/>
-      <x:c r="H16" s="8"/>
-      <x:c r="I16" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J16" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K16" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L16" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC8 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
@@ -9128,18 +11673,28 @@
       </x:c>
       <x:c r="F17" s="10"/>
       <x:c r="G17" s="10"/>
-      <x:c r="H17" s="8"/>
-      <x:c r="I17" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J17" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K17" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L17" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC9 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
@@ -9160,18 +11715,28 @@
       </x:c>
       <x:c r="F18" s="10"/>
       <x:c r="G18" s="10"/>
-      <x:c r="H18" s="8"/>
-      <x:c r="I18" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J18" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K18" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L18" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC10 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
@@ -9192,18 +11757,28 @@
       </x:c>
       <x:c r="F19" s="10"/>
       <x:c r="G19" s="10"/>
-      <x:c r="H19" s="8"/>
-      <x:c r="I19" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J19" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K19" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L19" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC11 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
@@ -9270,18 +11845,28 @@
       </x:c>
       <x:c r="F22" s="10"/>
       <x:c r="G22" s="10"/>
-      <x:c r="H22" s="8"/>
-      <x:c r="I22" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J22" s="8" t="str">
         <x:v>Mount reference</x:v>
       </x:c>
-      <x:c r="K22" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L22" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel PTC4 (2026-10-14); axial reference remains CAD-derived. XWALK/ASM-023: centerline fluid temperature is a working observation assumption, not a measured junction depth. User confirms Rev9 location. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
@@ -9302,18 +11887,28 @@
       </x:c>
       <x:c r="F23" s="10"/>
       <x:c r="G23" s="10"/>
-      <x:c r="H23" s="8"/>
-      <x:c r="I23" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J23" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K23" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L23" s="8" t="str">
-        <x:v>Multiple closest-point solutions; not a verified sensing junction.</x:v>
+      <x:c r="K23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC12 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. Multiple closest-point solutions; not a verified sensing junction. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
@@ -9366,18 +11961,28 @@
       </x:c>
       <x:c r="F25" s="10"/>
       <x:c r="G25" s="10"/>
-      <x:c r="H25" s="8"/>
-      <x:c r="I25" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J25" s="8" t="str">
         <x:v>Mount reference</x:v>
       </x:c>
-      <x:c r="K25" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L25" s="8" t="str">
-        <x:v>Actual sensing location and channel mapping unverified.</x:v>
+      <x:c r="K25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel PTC2 (2026-10-14); axial reference remains CAD-derived. XWALK/ASM-023: centerline fluid temperature is a working observation assumption, not a measured junction depth. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
@@ -9398,18 +12003,28 @@
       </x:c>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="10"/>
-      <x:c r="H26" s="8"/>
-      <x:c r="I26" s="8" t="str">
-        <x:v>CAD-derived</x:v>
+      <x:c r="H26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
       <x:c r="J26" s="8" t="str">
         <x:v>Pipe reference</x:v>
       </x:c>
-      <x:c r="K26" s="8" t="str">
-        <x:v>VCU-R9-E01 (2026-10-08) sheets 5-7</x:v>
-      </x:c>
-      <x:c r="L26" s="8" t="str">
-        <x:v>CAD body-to-pipe gap 1.0455 mm; contact unverified.</x:v>
+      <x:c r="K26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VCU-R9-E01 (2026-10-08) sheets 5-7; VSEL; WORK; XWALK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL/WORK: user-selected working channel STC1 (2026-10-14); axial reference remains CAD-derived. All STCs contact bare pipe locally; parent-region insulation remains per VREG. CAD body-to-pipe gap 1.0455 mm; contact unverified. Physical junction/attachment and historical run applicability remain unverified.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9556,10 +12171,20 @@
       <x:c r="G6" s="8"/>
       <x:c r="H6" s="8"/>
       <x:c r="I6" s="8"/>
-      <x:c r="J6" s="8"/>
-      <x:c r="K6" s="8"/>
-      <x:c r="L6" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
@@ -9574,10 +12199,20 @@
       <x:c r="G7" s="8"/>
       <x:c r="H7" s="8"/>
       <x:c r="I7" s="8"/>
-      <x:c r="J7" s="8"/>
-      <x:c r="K7" s="8"/>
-      <x:c r="L7" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
@@ -9592,10 +12227,20 @@
       <x:c r="G8" s="8"/>
       <x:c r="H8" s="8"/>
       <x:c r="I8" s="8"/>
-      <x:c r="J8" s="8"/>
-      <x:c r="K8" s="8"/>
-      <x:c r="L8" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
@@ -9610,10 +12255,20 @@
       <x:c r="G9" s="8"/>
       <x:c r="H9" s="8"/>
       <x:c r="I9" s="8"/>
-      <x:c r="J9" s="8"/>
-      <x:c r="K9" s="8"/>
-      <x:c r="L9" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
@@ -9646,10 +12301,20 @@
       <x:c r="G11" s="8"/>
       <x:c r="H11" s="8"/>
       <x:c r="I11" s="8"/>
-      <x:c r="J11" s="8"/>
-      <x:c r="K11" s="8"/>
-      <x:c r="L11" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L11" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
@@ -9664,10 +12329,20 @@
       <x:c r="G12" s="8"/>
       <x:c r="H12" s="8"/>
       <x:c r="I12" s="8"/>
-      <x:c r="J12" s="8"/>
-      <x:c r="K12" s="8"/>
-      <x:c r="L12" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
@@ -9682,10 +12357,20 @@
       <x:c r="G13" s="8"/>
       <x:c r="H13" s="8"/>
       <x:c r="I13" s="8"/>
-      <x:c r="J13" s="8"/>
-      <x:c r="K13" s="8"/>
-      <x:c r="L13" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L13" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
@@ -9718,10 +12403,20 @@
       <x:c r="G15" s="8"/>
       <x:c r="H15" s="8"/>
       <x:c r="I15" s="8"/>
-      <x:c r="J15" s="8"/>
-      <x:c r="K15" s="8"/>
-      <x:c r="L15" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L15" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
@@ -9736,10 +12431,20 @@
       <x:c r="G16" s="8"/>
       <x:c r="H16" s="8"/>
       <x:c r="I16" s="8"/>
-      <x:c r="J16" s="8"/>
-      <x:c r="K16" s="8"/>
-      <x:c r="L16" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L16" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
@@ -9754,10 +12459,20 @@
       <x:c r="G17" s="8"/>
       <x:c r="H17" s="8"/>
       <x:c r="I17" s="8"/>
-      <x:c r="J17" s="8"/>
-      <x:c r="K17" s="8"/>
-      <x:c r="L17" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
@@ -9772,10 +12487,20 @@
       <x:c r="G18" s="8"/>
       <x:c r="H18" s="8"/>
       <x:c r="I18" s="8"/>
-      <x:c r="J18" s="8"/>
-      <x:c r="K18" s="8"/>
-      <x:c r="L18" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
@@ -9790,10 +12515,20 @@
       <x:c r="G19" s="8"/>
       <x:c r="H19" s="8"/>
       <x:c r="I19" s="8"/>
-      <x:c r="J19" s="8"/>
-      <x:c r="K19" s="8"/>
-      <x:c r="L19" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
@@ -9840,10 +12575,20 @@
       <x:c r="G22" s="8"/>
       <x:c r="H22" s="8"/>
       <x:c r="I22" s="8"/>
-      <x:c r="J22" s="8"/>
-      <x:c r="K22" s="8"/>
-      <x:c r="L22" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L22" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
@@ -9858,10 +12603,20 @@
       <x:c r="G23" s="8"/>
       <x:c r="H23" s="8"/>
       <x:c r="I23" s="8"/>
-      <x:c r="J23" s="8"/>
-      <x:c r="K23" s="8"/>
-      <x:c r="L23" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L23" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
@@ -9894,10 +12649,20 @@
       <x:c r="G25" s="8"/>
       <x:c r="H25" s="8"/>
       <x:c r="I25" s="8"/>
-      <x:c r="J25" s="8"/>
-      <x:c r="K25" s="8"/>
-      <x:c r="L25" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Centerline fluid temperature at Rev9 axial reference, working assumption; mount is not a measured tip. XWALK/ASM-023; VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L25" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
@@ -9912,10 +12677,20 @@
       <x:c r="G26" s="8"/>
       <x:c r="H26" s="8"/>
       <x:c r="I26" s="8"/>
-      <x:c r="J26" s="8"/>
-      <x:c r="K26" s="8"/>
-      <x:c r="L26" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Outside pipe surface at Rev9 axial reference; local bare contact; physical junction unresolved. VSEL; WORK; XWALK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L26" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
@@ -9930,10 +12705,20 @@
       <x:c r="G27" s="8"/>
       <x:c r="H27" s="8"/>
       <x:c r="I27" s="8"/>
-      <x:c r="J27" s="8"/>
-      <x:c r="K27" s="8"/>
-      <x:c r="L27" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J27" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC6 = jacket outlet; port mount reference only; wetted measurement plane unknown. VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K27" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC6 = jacket outlet; port mount reference only; wetted measurement plane unknown. VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L27" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
@@ -9948,10 +12733,20 @@
       <x:c r="G28" s="8"/>
       <x:c r="H28" s="8"/>
       <x:c r="I28" s="8"/>
-      <x:c r="J28" s="8"/>
-      <x:c r="K28" s="8"/>
-      <x:c r="L28" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="J28" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC5 = jacket inlet; port mount reference only; wetted measurement plane unknown. VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K28" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC5 = jacket inlet; port mount reference only; wetted measurement plane unknown. VSEL; WORK.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L28" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Unknown</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10103,9 +12898,15 @@
       <x:c r="G7" s="8" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="H7" s="8"/>
-      <x:c r="I7" s="8" t="str">
-        <x:v>Enter verified energized start/end; add one row per element.</x:v>
+      <x:c r="H7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Measured energized boundaries remain unknown. Separate working model choice: full projected H-A span 0 to 1346.4962148518246 mm; not a clamp envelope or measured footprint.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
@@ -10126,9 +12927,15 @@
       <x:c r="G8" s="8" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="H8" s="8"/>
-      <x:c r="I8" s="8" t="str">
-        <x:v>Define independently of jacket envelope.</x:v>
+      <x:c r="H8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Active heat-transfer extent and routing unresolved. Mechanical jacket envelope is separate; PTC5/JTC-B inlet and PTC6/JTC-A outlet are user-selected working roles.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10257,11 +13064,17 @@
       <x:c r="E6" s="8" t="str">
         <x:v>Mass fraction</x:v>
       </x:c>
-      <x:c r="F6" s="8"/>
+      <x:c r="F6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Primary-loop candidate; select per run</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G6" s="10"/>
       <x:c r="H6" s="10"/>
-      <x:c r="I6" s="8" t="str">
-        <x:v>Product / formulation to verify</x:v>
+      <x:c r="I6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>USER; PG; FLUIDCFG; formulation/property model unqualified</x:t>
+        </x:is>
       </x:c>
       <x:c r="J6" s="8" t="str">
         <x:v>Reported</x:v>
@@ -10279,10 +13092,18 @@
       </x:c>
       <x:c r="D7" s="8"/>
       <x:c r="E7" s="8"/>
-      <x:c r="F7" s="8"/>
+      <x:c r="F7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Primary-loop option and room ambient; distinguish per run</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G7" s="10"/>
       <x:c r="H7" s="10"/>
-      <x:c r="I7" s="8"/>
+      <x:c r="I7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>USER; XWALK; ambient-named file does not establish air-filled loop (TRIAGE)</x:t>
+        </x:is>
+      </x:c>
       <x:c r="J7" s="8" t="str">
         <x:v>Reported</x:v>
       </x:c>
@@ -10299,10 +13120,18 @@
       </x:c>
       <x:c r="D8" s="8"/>
       <x:c r="E8" s="8"/>
-      <x:c r="F8" s="8"/>
+      <x:c r="F8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported jacket coolant; primary-loop option per run</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G8" s="10"/>
       <x:c r="H8" s="10"/>
-      <x:c r="I8" s="8"/>
+      <x:c r="I8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>USER; XWALK; WORK; coolant circuit reported; properties unselected</x:t>
+        </x:is>
+      </x:c>
       <x:c r="J8" s="8" t="str">
         <x:v>Reported</x:v>
       </x:c>
@@ -10730,83 +13559,213 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="8" t="str">
-        <x:v>TLEP and expansion tank</x:v>
-      </x:c>
-      <x:c r="B6" s="8"/>
-      <x:c r="C6" s="8"/>
-      <x:c r="D6" s="8"/>
-      <x:c r="E6" s="8" t="str">
-        <x:v>Confirm level, vent/pressure, connectivity and thermal coupling.</x:v>
-      </x:c>
-      <x:c r="F6" s="8"/>
-      <x:c r="G6" s="8"/>
-      <x:c r="H6" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="A6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>TLEP and expansion tank</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Installed state unverified</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Shared default ASM-021 retains top exit with experiment-specific temperature/pressure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Select physical termination and reservoir coupling explicitly; not an installed boundary assignment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>ASSUME ASM-021; CAD dimensions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>No pressure, tank level, vent state or thermal coupling selected.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Assumed</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="8" t="str">
-        <x:v>BREP and drain</x:v>
-      </x:c>
-      <x:c r="B7" s="8"/>
-      <x:c r="C7" s="8"/>
-      <x:c r="D7" s="8"/>
-      <x:c r="E7" s="8" t="str">
-        <x:v>Confirm valve state, termination plane and thermal coupling.</x:v>
-      </x:c>
-      <x:c r="F7" s="8"/>
-      <x:c r="G7" s="8"/>
-      <x:c r="H7" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="A7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>BREP and drain</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Installed valve state unverified</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Shared default ASM-020 omits bottom exit; this is a model-domain choice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Explicitly define omitted branch or physical termination and thermal losses</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>ASSUME ASM-020; CAD dimensions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>No evidence that omitted means physically sealed or adiabatic.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Assumed</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="8" t="str">
-        <x:v>Heater power</x:v>
-      </x:c>
-      <x:c r="B8" s="8"/>
-      <x:c r="C8" s="8"/>
-      <x:c r="D8" s="8"/>
-      <x:c r="E8" s="8" t="str">
-        <x:v>Electrical heater evidence conflicts with draft secondary-heater plan.</x:v>
-      </x:c>
-      <x:c r="F8" s="8"/>
-      <x:c r="G8" s="8"/>
-      <x:c r="H8" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="A8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Heater power</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Electrical mat/band heating reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Integrate applied input to eta_heater times measured electrical power; eta and power unselected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Document element footprint, electrical metering, storage and external losses</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>HEAT; VSEL; Requirements C34-C37/M08</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Voltage setting is not watts. No measured spatial split/efficiency or net duty supplied.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="8" t="str">
-        <x:v>Cooler control</x:v>
-      </x:c>
-      <x:c r="B9" s="8"/>
-      <x:c r="C9" s="8"/>
-      <x:c r="D9" s="8"/>
-      <x:c r="E9" s="8" t="str">
-        <x:v>Document coolant flow, inlet temperature, feedback and measurement planes.</x:v>
-      </x:c>
-      <x:c r="F9" s="8"/>
-      <x:c r="G9" s="8"/>
-      <x:c r="H9" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="A9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Cooler control</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>User reports chiller on/off contributes to hot-plateau oscillations</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Use run-specific measured PTC5 inlet/flow when available; retain cyclic forcing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Resolve jacket route/active span and measured inlet/flow before selecting boundary</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>OPCYCLE; FOLLOW; VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>PTC6 outlet is comparison/energy-balance information, not another arbitrary imposed boundary. Switching times and controller identity unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="8" t="str">
-        <x:v>External convection / radiation</x:v>
-      </x:c>
-      <x:c r="B10" s="8"/>
-      <x:c r="C10" s="8"/>
-      <x:c r="D10" s="8"/>
-      <x:c r="E10" s="8" t="str">
-        <x:v>Document room environment, coverings, surfaces and supports.</x:v>
-      </x:c>
-      <x:c r="F10" s="8"/>
-      <x:c r="G10" s="8"/>
-      <x:c r="H10" s="8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="A10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>External convection / radiation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Straight D-E bare; all STC contacts locally bare; remaining regions per VREG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Separate coolant exchange under jacket from room-air losses; coefficient/emissivity unselected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Resolve local surfaces, supports and coverings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VREG; CURRENT; VSEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Local bare STC contact does not make whole parent leg bare. Ambient XYZ/RH and support conductances unknown.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
@@ -10954,6 +13913,216 @@
       <x:c r="H16" s="8" t="inlineStr">
         <x:is>
           <x:t>Modeling assumption</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Working sensor observation operators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>16 numbered main channels; two jacket channels</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC outside wall; PTC1-4 centerline fluid assumption; PTC5 inlet/PTC6 outlet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Use matching physical layer; do not interpret mount centroid as sensing junction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; XWALK; ASSUME ASM-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>LF optical extent and binding unknown; Amb/Tank coordinates unknown; Type B calibration unqualified.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Assumed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Frame and gravity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Rev9 drawing frame B origin; x=B_CAD_Z-CAD_Z; y=CAD_Y-B_CAD_Y; n=CAD_X-B_CAD_X</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Working local gravity (0,-1,0); derive inclination from geometry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Retain n for ports/branches and qualify gravity against installed survey</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Working geometry convention, not independently measured gravity. No physical sensor angles inferred.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Assumed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Insulation contact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Perfect contact was user-directed model assumption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Perfect pipe/insulation contact candidate; preserve local bare STCs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Contact resistance/attachment and support details require survey</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VINS; ASSUME; VSEL; CURRENT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Perfect contact is not measured; thickness/material uncertainties remain unquantified.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Assumed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Historical configuration applicability</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>STC5 moved; change date not supplied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Retain original Rev8 configurations for historical computed results</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Do not relabel old meshes/results as Rev9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>VSEL; WORK; FOLLOW</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>No run-to-installation validity dates supplied. This workbook does not activate solver migration.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Data validity and uncertainty</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>June12 STC6/PTC2/PTC3 have nonphysical data; slow temporal correlation present</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Use source-hashed interval masks and temporal-block/covariance checks; keep raw immutable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Apply same observation/validity/uncertainty contract</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>DAQISS; FOLLOW; DIAG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Diagnostics are not Type B accuracy or accepted steady windows. July29 has no readable waveform.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Computational + experimental review</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Reported</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/VCU_inputs.xlsx
+++ b/VCU_inputs.xlsx
@@ -2549,11 +2549,7 @@
       <x:c r="A16" s="8" t="str">
         <x:v>Prepared by</x:v>
       </x:c>
-      <x:c r="B16" s="9" t="inlineStr">
-        <x:is>
-          <x:t>Codex / agent-root-cfg002; requested by Andres Fierro</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B16" s="9"/>
       <x:c r="C16" s="8" t="str">
         <x:v>Enter name.</x:v>
       </x:c>
